--- a/cartographie/CREATEURS_NOMMES_PAR_LES_LOBBIES.xlsx
+++ b/cartographie/CREATEURS_NOMMES_PAR_LES_LOBBIES.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,8 @@
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,58 +527,58 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Une seule question, colonne verte : est-ce un createur de contenu, ou autre chose ?</t>
+          <t>Deux questions, colonnes vertes.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Est-ce un createur de contenu, ou autre chose ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Quel type de personne ? (createur, chef, eleveur, personnalite TV...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Beaucoup de ces noms sont des titres de series (« Milk Check ») ou des labels (« Label Rouge »). L'outil ne sait pas les distinguer.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>POURQUOI CA COMPTE</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>L'outil a deux facons de reconnaitre un nom, indiquee colonne « Comment on l'a trouve ».</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Tes reponses mesureront ce que chacune vaut. Si « motif dans le titre » ne donne que des series, on l'abandonne.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Les lignes sur fond gris viennent de cette voie-la, les blanches de l'autre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>TU PEUX T'ARRETER EN COURS DE ROUTE</t>
         </is>
       </c>
     </row>
@@ -587,24 +588,28 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Les lignes sont triees par valeur : les plus solides en haut. Juger les 60 premieres suffit a mesurer les deux voies.</t>
+          <t>La SECONDE question sert a tout autre chose : savoir quelle part des collaborations le projet voit.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Le reste est la pour ne rien perdre, pas pour t'occuper une soiree.</t>
+          <t>Nos deux methodes trouvent 36 et 42 createurs, et n'ont qu'UN nom en commun. Soit on rate enormement, soit les deux methodes cherchent des gens differents.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Si ces 42 noms sont surtout des chefs et des eleveurs, c'est la seconde explication. S'ils ressemblent aux youtubeurs qu'on trouve par ailleurs, c'est la premiere — et notre couverture est mauvaise.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>ATTENTION</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Les lignes sur fond gris viennent de cette voie-la, les blanches de l'autre.</t>
         </is>
       </c>
     </row>
@@ -612,377 +617,139 @@
       <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Etre nomme par un lobby etablit une collaboration, PAS une remuneration. La question du paiement vient apres.</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>TU PEUX T'ARRETER EN COURS DE ROUTE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Les lignes sont triees par valeur : les plus solides en haut. Juger les 60 premieres suffit a mesurer les deux voies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Le reste est la pour ne rien perdre, pas pour t'occuper une soiree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ATTENTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Etre nomme par un lobby etablit une collaboration, PAS une remuneration. La question du paiement vient apres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Nom trouve</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Commanditaire</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Comment on l'a trouve</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Videos</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Titre de la video</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Regarder</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>EST-CE UN CREATEUR ?</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>QUEL TYPE DE PERSONNE ?</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>Ton commentaire</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Pierre Chomet</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>CIFOG, CNIEL</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « Pierre Chomet »</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2022-03-17</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>La Volaille Française</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>ANVOL</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « La Volaille Française »</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>La Volaille Française vous souhaite une bonne année 2026 !</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Morgan VS</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « Morgan VS »</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>L’Amour Bœuf</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « L’Amour Bœuf »</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Les produits tripiers</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « produitstripiers »</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2016-03-02</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Dominique Groussard, Artisan Tripier 05 - Les produits tripiers pour les néophytes</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Label Rouge</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « Label Rouge »</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Sonia et Romain, éleveurs de bœufs Label Rouge en Auvergne</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Fabrice Mignot</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>compte connu, reconnu sur « Fabrice Mignot »</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2016-02-28</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Fabrice Mignot, Chef 02 - Recette express de tournedos de cheval façon Rossini</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>voir la video</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Pierre Chomet</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>CIFOG, INTERBEV</t>
+          <t>CIFOG, CNIEL</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Christian »</t>
+          <t>compte connu, reconnu sur « Pierre Chomet »</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2013-07-17</t>
+          <t>2022-03-17</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Traçabilité - Christian Etchebest - Connaître l'origine de la viande en restauration</t>
+          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -992,37 +759,38 @@
       </c>
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>e-Boucherie normande</t>
+          <t>La Volaille Française</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « tabledeseleveurs »</t>
+          <t>compte connu, reconnu sur « La Volaille Française »</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Sonia et Romain, éleveurs de bœufs Label Rouge en Auvergne</t>
+          <t>La Volaille Française vous souhaite une bonne année 2026 !</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1032,37 +800,38 @@
       </c>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>La Brigade</t>
+          <t>Morgan VS</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>CIFOG, CNIEL</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « La Brigade »</t>
+          <t>compte connu, reconnu sur « Morgan VS »</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode 5 (avec Philippine Jaillet)</t>
+          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -1072,37 +841,38 @@
       </c>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Salon International de l'Agriculture</t>
+          <t>L’Amour Bœuf</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>CNIEL, INTERBEV</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Salon International de l'Agriculture »</t>
+          <t>compte connu, reconnu sur « L’Amour Bœuf »</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>La France, terre de lait - la Filière laitière française en chiffres</t>
+          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -1112,37 +882,38 @@
       </c>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>✿ 𝑨𝒍𝒆𝒙𝒂𝒏𝒅𝒓𝒂 ✿</t>
+          <t>Les produits tripiers</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « ✿ 𝑨𝒍𝒆𝒙𝒂𝒏𝒅𝒓𝒂 ✿ »</t>
+          <t>compte connu, reconnu sur « produitstripiers »</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>MISTER V - LES COPAINS AU LAIT - EP.3 LE SKA</t>
+          <t>Dominique Groussard, Artisan Tripier 05 - Les produits tripiers pour les néophytes</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -1152,37 +923,38 @@
       </c>
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Brigitte Lecordier</t>
+          <t>Label Rouge</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Brigitte Lecordier »</t>
+          <t>compte connu, reconnu sur « Label Rouge »</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Pub Les Produits Laitiers Manga - Filière Laitière</t>
+          <t>Sonia et Romain, éleveurs de bœufs Label Rouge en Auvergne</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -1192,14 +964,15 @@
       </c>
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Bertrand</t>
+          <t>Fabrice Mignot</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1209,20 +982,20 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Bertrand »</t>
+          <t>compte connu, reconnu sur « Fabrice Mignot »</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
+          <t>2016-02-28</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Interview Métiers - Bertrand, chef cuisinier en restauration scolaire</t>
+          <t>Fabrice Mignot, Chef 02 - Recette express de tournedos de cheval façon Rossini</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -1232,37 +1005,38 @@
       </c>
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Chef Pâtissier</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG, INTERBEV</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « La Brigade »</t>
+          <t>compte connu, reconnu sur « Christian »</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2013-07-17</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
+          <t>Traçabilité - Christian Etchebest - Connaître l'origine de la viande en restauration</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -1272,37 +1046,38 @@
       </c>
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Gino Catena</t>
+          <t>e-Boucherie normande</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Gino Catena »</t>
+          <t>compte connu, reconnu sur « tabledeseleveurs »</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Volaillissimes - Marché de gros : rencontre avec Gino Catena (version courte)</t>
+          <t>Sonia et Romain, éleveurs de bœufs Label Rouge en Auvergne</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -1312,37 +1087,38 @@
       </c>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Ile de France</t>
+          <t>La Brigade</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG, CNIEL</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Ile de France »</t>
+          <t>compte connu, reconnu sur « La Brigade »</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri (version courte)</t>
+          <t>CHAUD! - Épisode 5 (avec Philippine Jaillet)</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -1352,37 +1128,38 @@
       </c>
       <c r="I44" s="7" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Jeffrey Cagnes</t>
+          <t>Salon International de l'Agriculture</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CNIEL, INTERBEV</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « jeffreycagnes »</t>
+          <t>compte connu, reconnu sur « Salon International de l'Agriculture »</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
+          <t>La France, terre de lait - la Filière laitière française en chiffres</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -1392,37 +1169,38 @@
       </c>
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Laura Martinez</t>
+          <t>✿ 𝑨𝒍𝒆𝒙𝒂𝒏𝒅𝒓𝒂 ✿</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « lauramartinez_dieteticienne »</t>
+          <t>compte connu, reconnu sur « ✿ 𝑨𝒍𝒆𝒙𝒂𝒏𝒅𝒓𝒂 ✿ »</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Bien manger pour bien bouger - LIVE Voiron</t>
+          <t>MISTER V - LES COPAINS AU LAIT - EP.3 LE SKA</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -1432,37 +1210,38 @@
       </c>
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>laviandetv</t>
+          <t>Brigitte Lecordier</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « laviandetv »</t>
+          <t>compte connu, reconnu sur « Brigitte Lecordier »</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Interview de Marine Le Pen - Salon de l'agriculture 2014</t>
+          <t>Pub Les Produits Laitiers Manga - Filière Laitière</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -1472,24 +1251,25 @@
       </c>
       <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Maison Terrasson</t>
+          <t>Bertrand</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Maison Terrasson »</t>
+          <t>compte connu, reconnu sur « Bertrand »</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -1497,12 +1277,12 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2014-05-26</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson (version courte)</t>
+          <t>Interview Métiers - Bertrand, chef cuisinier en restauration scolaire</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -1512,24 +1292,25 @@
       </c>
       <c r="I48" s="7" t="inlineStr"/>
       <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Omnivore</t>
+          <t>Chef Pâtissier</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Omnivore »</t>
+          <t>compte connu, reconnu sur « La Brigade »</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -1537,12 +1318,12 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Campagne collective "Aimez la viande Mangez-en mieux" signée "Celles et ceux qui font la viande"</t>
+          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -1552,24 +1333,25 @@
       </c>
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>p h i l i p p e</t>
+          <t>Gino Catena</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>CIFOG, INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « p h i l i p p e »</t>
+          <t>compte connu, reconnu sur « Gino Catena »</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -1577,12 +1359,12 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 2 - Autonomie alimentaire avec Philippe SELLIER</t>
+          <t>Volaillissimes - Marché de gros : rencontre avec Gino Catena (version courte)</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -1592,24 +1374,25 @@
       </c>
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Tour de France</t>
+          <t>Ile de France</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Tour de France »</t>
+          <t>compte connu, reconnu sur « Ile de France »</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -1617,12 +1400,12 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Bien manger pour bien bouger - LIVE Voiron</t>
+          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri (version courte)</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -1632,37 +1415,38 @@
       </c>
       <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Anne . Papilles et Pupilles</t>
+          <t>Jeffrey Cagnes</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « papilles »</t>
+          <t>compte connu, reconnu sur « jeffreycagnes »</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - l’entrecôte</t>
+          <t>CHAUD! - Épisode final (avec Morgan VS, GMK et Ragnar Le Breton)</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -1672,14 +1456,15 @@
       </c>
       <c r="I52" s="7" t="inlineStr"/>
       <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Anne Reverdy</t>
+          <t>Laura Martinez</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1689,20 +1474,20 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « panier_de_saison »</t>
+          <t>compte connu, reconnu sur « lauramartinez_dieteticienne »</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Entretien avec Anne du blog Panier de Saison</t>
+          <t>Bien manger pour bien bouger - LIVE Voiron</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -1712,37 +1497,38 @@
       </c>
       <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>laviandetv</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Benjamin »</t>
+          <t>compte connu, reconnu sur « laviandetv »</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>DANS NOS ASSIETTES - BENJAMIN</t>
+          <t>Interview de Marine Le Pen - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -1752,37 +1538,38 @@
       </c>
       <c r="I54" s="7" t="inlineStr"/>
       <c r="J54" s="7" t="inlineStr"/>
+      <c r="K54" s="7" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>BiodiversiTerre</t>
+          <t>Maison Terrasson</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « BiodiversiTerre »</t>
+          <t>compte connu, reconnu sur « Maison Terrasson »</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2017-09-05</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>BiodiversiTerre</t>
+          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson (version courte)</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -1792,14 +1579,15 @@
       </c>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>BLANDINE</t>
+          <t>Omnivore</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1809,20 +1597,20 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « BLANDINE »</t>
+          <t>compte connu, reconnu sur « Omnivore »</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2013-09-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Débat sur la transmission culinaire - C'est pas tranché!</t>
+          <t>Campagne collective "Aimez la viande Mangez-en mieux" signée "Celles et ceux qui font la viande"</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -1832,37 +1620,38 @@
       </c>
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Boucherie Charcuterie A.mareau</t>
+          <t>p h i l i p p e</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG, INTERBEV</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « boucherie.a »</t>
+          <t>compte connu, reconnu sur « p h i l i p p e »</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2022-04-04</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Nicolas Pegheaire, 25 ans:Les Nouveaux visages de la filière élevage et viande de Nouvelle-Aquitaine</t>
+          <t>BIEN ÉLEVÉE ! Émission 2 - Autonomie alimentaire avec Philippe SELLIER</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -1872,14 +1661,15 @@
       </c>
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Charline</t>
+          <t>Tour de France</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1889,20 +1679,20 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Charline »</t>
+          <t>compte connu, reconnu sur « Tour de France »</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2015-08-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Entretien avec Charline Picon - Championne du Monde RS:X 2014 - Planche à voile olympique</t>
+          <t>Bien manger pour bien bouger - LIVE Voiron</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -1912,14 +1702,15 @@
       </c>
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Dévore des Yeux</t>
+          <t>Anne . Papilles et Pupilles</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1929,7 +1720,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Dévore des Yeux »</t>
+          <t>compte connu, reconnu sur « papilles »</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -1937,12 +1728,12 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Entretien avec Anne du blog Panier de Saison</t>
+          <t>L’Amour Bœuf - l’entrecôte</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -1952,14 +1743,15 @@
       </c>
       <c r="I59" s="7" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Fabien Patanchon</t>
+          <t>Anne Reverdy</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1969,7 +1761,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Fabien Patanchon »</t>
+          <t>compte connu, reconnu sur « panier_de_saison »</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -1977,12 +1769,12 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2014-12-19</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Bien manger pour bien bouger - LIVE Bordeaux</t>
+          <t>Entretien avec Anne du blog Panier de Saison</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -1992,24 +1784,25 @@
       </c>
       <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Floriane</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Floriane »</t>
+          <t>compte connu, reconnu sur « Benjamin »</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -2017,12 +1810,12 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
+          <t>DANS NOS ASSIETTES - BENJAMIN</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -2032,24 +1825,25 @@
       </c>
       <c r="I61" s="7" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Fromaville - Yaourterie artisanale</t>
+          <t>BiodiversiTerre</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « fromaville »</t>
+          <t>compte connu, reconnu sur « BiodiversiTerre »</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -2057,12 +1851,12 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2017-09-05</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>LES STAGIAIRES (AVEC OCÉANE, LE MOTIF, JOËL ET YASSENCORE)</t>
+          <t>BiodiversiTerre</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -2072,14 +1866,15 @@
       </c>
       <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" s="7" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>LeStream</t>
+          <t>BLANDINE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2089,7 +1884,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « LeStream »</t>
+          <t>compte connu, reconnu sur « BLANDINE »</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -2097,12 +1892,12 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2013-09-27</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Gamestronomie Vlog #1 - Lutti</t>
+          <t>Débat sur la transmission culinaire - C'est pas tranché!</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -2112,24 +1907,25 @@
       </c>
       <c r="I63" s="7" t="inlineStr"/>
       <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Mehdi Maïzi</t>
+          <t>Boucherie Charcuterie A.mareau</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Mehdi Maïzi »</t>
+          <t>compte connu, reconnu sur « boucherie.a »</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -2137,12 +1933,12 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2022-04-04</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>QUIZZ’IN AVEC MEHDI MAÏZI, SOSO MANESS, KAMETO, BIG COLOMBIEN ET YANNOU JR</t>
+          <t>Nicolas Pegheaire, 25 ans:Les Nouveaux visages de la filière élevage et viande de Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -2152,24 +1948,25 @@
       </c>
       <c r="I64" s="7" t="inlineStr"/>
       <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Redouane Bougheraba</t>
+          <t>Charline</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Redouane Bougheraba »</t>
+          <t>compte connu, reconnu sur « Charline »</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -2177,12 +1974,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2022-03-17</t>
+          <t>2015-08-21</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
+          <t>Entretien avec Charline Picon - Championne du Monde RS:X 2014 - Planche à voile olympique</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -2192,24 +1989,25 @@
       </c>
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Romuald Fassenet</t>
+          <t>Dévore des Yeux</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Romuald Fassenet »</t>
+          <t>compte connu, reconnu sur « Dévore des Yeux »</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -2217,12 +2015,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2014-12-19</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Morgan VS découvre les AOP : le Comté</t>
+          <t>Entretien avec Anne du blog Panier de Saison</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -2232,24 +2030,25 @@
       </c>
       <c r="I66" s="7" t="inlineStr"/>
       <c r="J66" s="7" t="inlineStr"/>
+      <c r="K66" s="7" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>The Best🥇 أستغفر الله</t>
+          <t>Fabien Patanchon</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « cedricdoumbe »</t>
+          <t>compte connu, reconnu sur « Fabien Patanchon »</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -2257,12 +2056,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>PETIT CAFÉ BRIOCHE 2 AVEC MISTER V, AMINE, CÉDRIC DOUMBÉ, GOLO &amp; RITCHIE</t>
+          <t>Bien manger pour bien bouger - LIVE Bordeaux</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -2272,24 +2071,25 @@
       </c>
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Théo Juice</t>
+          <t>Floriane</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « Théo Juice »</t>
+          <t>compte connu, reconnu sur « Floriane »</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -2297,12 +2097,12 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2018-11-23</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Les Produits Laitiers sont nos amis pour la vie - Mister V</t>
+          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -2312,24 +2112,25 @@
       </c>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" s="7" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>• Tiphaine • 🥣🍷🍪📷</t>
+          <t>Fromaville - Yaourterie artisanale</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>compte connu, reconnu sur « gourmandiseries »</t>
+          <t>compte connu, reconnu sur « fromaville »</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
@@ -2337,12 +2138,12 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Entretien avec Tiphaine du blog Gourmandiseries</t>
+          <t>LES STAGIAIRES (AVEC OCÉANE, LE MOTIF, JOËL ET YASSENCORE)</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -2352,299 +2153,307 @@
       </c>
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Interview Métiers</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="A70" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>LeStream</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>INTERBEV</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>Interview Métiers - Véronique, éleveuse de bovins</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « LeStream »</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Gamestronomie Vlog #1 - Lutti</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Histoire Métiers</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>Histoire Métiers - Xavier, éleveur d'équins</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="A71" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Mehdi Maïzi</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « Mehdi Maïzi »</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>QUIZZ’IN AVEC MEHDI MAÏZI, SOSO MANESS, KAMETO, BIG COLOMBIEN ET YANNOU JR</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Nos Chefs nous manquent</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>CIFOG</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>Nos Chefs nous manquent - Episode 8 : Mathieu Fauquembergue</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="A72" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Redouane Bougheraba</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « Redouane Bougheraba »</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2022-03-17</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
       <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="7" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>MIV 2021</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>MIV 2021 - Dominique, chef en restauration scolaire</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="A73" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Romuald Fassenet</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « Romuald Fassenet »</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-08</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Morgan VS découvre les AOP : le Comté</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>Made in viande 2014</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>2015-02-03</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>Made in viande 2014 - Commercialisation</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="A74" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>The Best🥇 أستغفر الله</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « cedricdoumbe »</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>PETIT CAFÉ BRIOCHE 2 AVEC MISTER V, AMINE, CÉDRIC DOUMBÉ, GOLO &amp; RITCHIE</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Chorégraphie</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>2017-05-19</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>Chorégraphie - Gaston le mouton</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="A75" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Théo Juice</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « Théo Juice »</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>2018-11-23</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Les Produits Laitiers sont nos amis pour la vie - Mister V</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>Et si on en parlait</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>motif dans le titre</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>Et si on en parlait : Les jus végétaux</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="A76" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>• Tiphaine • 🥣🍷🍪📷</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>compte connu, reconnu sur « gourmandiseries »</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>2014-12-19</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Entretien avec Tiphaine du blog Gourmandiseries</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>voir la video</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="7" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="8" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Génération XYZ</t>
+          <t>Interview Métiers</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -2653,16 +2462,16 @@
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2014-05-26</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Génération XYZ - Damien, producer of Foie Gras in short circuit and direct sale</t>
+          <t>Interview Métiers - Véronique, éleveuse de bovins</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
@@ -2672,14 +2481,15 @@
       </c>
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="8" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>La Sauce de la Paix</t>
+          <t>Histoire Métiers</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -2693,16 +2503,16 @@
         </is>
       </c>
       <c r="E78" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2014-05-26</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>La Sauce de la Paix - Naturellement Flexitariens</t>
+          <t>Histoire Métiers - Xavier, éleveur d'équins</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -2712,19 +2522,20 @@
       </c>
       <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr"/>
+      <c r="K78" s="7" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="8" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Milk Check</t>
+          <t>Nos Chefs nous manquent</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -2733,16 +2544,16 @@
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Milk Check : C’est vrai que certains adultes ne digèrent pas le lait ?</t>
+          <t>Nos Chefs nous manquent - Episode 8 : Mathieu Fauquembergue</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -2752,19 +2563,20 @@
       </c>
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="8" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Nos amis pour la vie</t>
+          <t>MIV 2021</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -2773,16 +2585,16 @@
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Nos amis pour la vie - version 1 - 1981</t>
+          <t>MIV 2021 - Dominique, chef en restauration scolaire</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -2792,19 +2604,20 @@
       </c>
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr"/>
+      <c r="K80" s="7" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="8" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Des sensations pures</t>
+          <t>Made in viande 2014</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -2813,16 +2626,16 @@
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>2011-06-29</t>
+          <t>2015-02-03</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Des sensations pures - la plongée - 1998</t>
+          <t>Made in viande 2014 - Commercialisation</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -2832,19 +2645,20 @@
       </c>
       <c r="I81" s="7" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Grand Voyage</t>
+          <t>Chorégraphie</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -2853,16 +2667,16 @@
         </is>
       </c>
       <c r="E82" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
+          <t>2017-05-19</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Milk Moments 2017</t>
+          <t>Chorégraphie - Gaston le mouton</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -2872,19 +2686,20 @@
       </c>
       <c r="I82" s="7" t="inlineStr"/>
       <c r="J82" s="7" t="inlineStr"/>
+      <c r="K82" s="7" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="8" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Et si on en parlait</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -2893,16 +2708,16 @@
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Interview - Taig Khris, parrain de l'univers "La Planète, les Hommes, les Bêtes"</t>
+          <t>Et si on en parlait : Les jus végétaux</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -2912,19 +2727,20 @@
       </c>
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="8" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Mister V</t>
+          <t>Génération XYZ</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -2933,16 +2749,16 @@
         </is>
       </c>
       <c r="E84" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>PETIT CAFÉ BRIOCHE 2 AVEC MISTER V, AMINE, CÉDRIC DOUMBÉ, GOLO &amp; RITCHIE</t>
+          <t>Génération XYZ - Damien, producer of Foie Gras in short circuit and direct sale</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -2952,19 +2768,20 @@
       </c>
       <c r="I84" s="7" t="inlineStr"/>
       <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="8" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>MISTER V</t>
+          <t>La Sauce de la Paix</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -2973,16 +2790,16 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>MISTER V - LES COPAINS AU LAIT - EP.3 LE SKA</t>
+          <t>La Sauce de la Paix - Naturellement Flexitariens</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -2992,19 +2809,20 @@
       </c>
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="8" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Nathalie de Masterchef Nathal</t>
+          <t>Milk Check</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -3013,16 +2831,16 @@
         </is>
       </c>
       <c r="E86" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>2013-12-04</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Magret de canard et son Foie Gras poêlé à l'émulsion de bière brune par Nathalie de Masterchef</t>
+          <t>Milk Check : C’est vrai que certains adultes ne digèrent pas le lait ?</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -3032,19 +2850,20 @@
       </c>
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="7" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="8" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>On the road to Foie Gras</t>
+          <t>Nos amis pour la vie</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -3053,16 +2872,16 @@
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>On the road to Foie Gras - E6 : Foie Gras: from the lobe to the plate!</t>
+          <t>Nos amis pour la vie - version 1 - 1981</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -3072,14 +2891,15 @@
       </c>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="8" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Pures sensations</t>
+          <t>Des sensations pures</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -3102,7 +2922,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Pures sensations - version mer - 2003</t>
+          <t>Des sensations pures - la plongée - 1998</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -3112,19 +2932,20 @@
       </c>
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="8" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Concours</t>
+          <t>Grand Voyage</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -3133,16 +2954,16 @@
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2017-10-30</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>Concours: Les Ardoises de Nouvelle-Aquitaine - édition 4 - Présentation</t>
+          <t>Milk Moments 2017</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -3152,19 +2973,20 @@
       </c>
       <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="8" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>DANS NOS ASSIETTES</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -3173,16 +2995,16 @@
         </is>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>DANS NOS ASSIETTES - BENJAMIN</t>
+          <t>Interview - Taig Khris, parrain de l'univers "La Planète, les Hommes, les Bêtes"</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -3192,19 +3014,20 @@
       </c>
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="8" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in pictures</t>
+          <t>Mister V</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -3213,16 +3036,16 @@
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in pictures : a meeting with Foie Gras producers - Japanese, with English subtitles</t>
+          <t>PETIT CAFÉ BRIOCHE 2 AVEC MISTER V, AMINE, CÉDRIC DOUMBÉ, GOLO &amp; RITCHIE</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -3232,19 +3055,20 @@
       </c>
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="8" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Jean Sorhouet</t>
+          <t>MISTER V</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -3253,16 +3077,16 @@
         </is>
       </c>
       <c r="E92" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Quels sont les intérêts pour les éleveurs-coopérateurs de contractualiser ?</t>
+          <t>MISTER V - LES COPAINS AU LAIT - EP.3 LE SKA</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -3272,19 +3096,20 @@
       </c>
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="8" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Le lait c'est gai</t>
+          <t>Nathalie de Masterchef Nathal</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -3293,16 +3118,16 @@
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2013-12-04</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Le lait c'est gai - 1984</t>
+          <t>Magret de canard et son Foie Gras poêlé à l'émulsion de bière brune par Nathalie de Masterchef</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -3312,19 +3137,20 @@
       </c>
       <c r="I93" s="7" t="inlineStr"/>
       <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="8" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>MADE in VIANDE 2017</t>
+          <t>On the road to Foie Gras</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -3333,16 +3159,16 @@
         </is>
       </c>
       <c r="E94" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>2017-04-28</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>MADE in VIANDE 2017 - Teaser 02</t>
+          <t>On the road to Foie Gras - E6 : Foie Gras: from the lobe to the plate!</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -3352,19 +3178,20 @@
       </c>
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="8" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Matthias Marc et Pierre Chome</t>
+          <t>Pures sensations</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -3373,16 +3200,16 @@
         </is>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2011-06-29</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
+          <t>Pures sensations - version mer - 2003</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -3392,19 +3219,20 @@
       </c>
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="8" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Concours</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -3417,12 +3245,12 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Rencontres sur la route du Foie Gras - E6 :  Le Foie Gras : du lobe à l’assiette !</t>
+          <t>Concours: Les Ardoises de Nouvelle-Aquitaine - édition 4 - Présentation</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -3432,14 +3260,15 @@
       </c>
       <c r="I96" s="7" t="inlineStr"/>
       <c r="J96" s="7" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="8" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle pub</t>
+          <t>DANS NOS ASSIETTES</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -3457,12 +3286,12 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>2012-01-27</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle pub - 3 produits laitiers par jour - 20s</t>
+          <t>DANS NOS ASSIETTES - BENJAMIN</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -3472,14 +3301,15 @@
       </c>
       <c r="I97" s="7" t="inlineStr"/>
       <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="8" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet Foie Gras poêlé</t>
+          <t>Foie Gras in pictures</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -3497,12 +3327,12 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels - E4 - Pinchos de Foie Gras poêlé par Pierre Chomet</t>
+          <t>Foie Gras in pictures : a meeting with Foie Gras producers - Japanese, with English subtitles</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -3512,19 +3342,20 @@
       </c>
       <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="8" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Pub TV</t>
+          <t>Jean Sorhouet</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -3537,12 +3368,12 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Pub TV - Les Produits Laitiers Manga - Environnement</t>
+          <t>Quels sont les intérêts pour les éleveurs-coopérateurs de contractualiser ?</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -3552,19 +3383,20 @@
       </c>
       <c r="I99" s="7" t="inlineStr"/>
       <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Recette Cuisine Viande</t>
+          <t>Le lait c'est gai</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
@@ -3577,12 +3409,12 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>2013-07-05</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Recette Cuisine Viande - Cœur de veau farci et carottes au cumin</t>
+          <t>Le lait c'est gai - 1984</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -3592,14 +3424,15 @@
       </c>
       <c r="I100" s="7" t="inlineStr"/>
       <c r="J100" s="7" t="inlineStr"/>
+      <c r="K100" s="7" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="8" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Recette de Cuisine Viande</t>
+          <t>MADE in VIANDE 2017</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -3617,12 +3450,12 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
+          <t>2017-04-28</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Recette de Cuisine Viande - Rôti de viande chevaline</t>
+          <t>MADE in VIANDE 2017 - Teaser 02</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -3632,19 +3465,20 @@
       </c>
       <c r="I101" s="7" t="inlineStr"/>
       <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="8" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Spot radio</t>
+          <t>Matthias Marc et Pierre Chome</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -3657,12 +3491,12 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Spot radio - VOLAILLE FRANCAISE</t>
+          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -3672,19 +3506,20 @@
       </c>
       <c r="I102" s="7" t="inlineStr"/>
       <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="7" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Stéphanie Sardain et Vincent</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -3697,12 +3532,12 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Volaillers : rencontre avec Stéphanie Sardain et Vincent Dumontet (version courte)</t>
+          <t>Rencontres sur la route du Foie Gras - E6 :  Le Foie Gras : du lobe à l’assiette !</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -3712,19 +3547,20 @@
       </c>
       <c r="I103" s="7" t="inlineStr"/>
       <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="8" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Traçabilité</t>
+          <t>Nouvelle pub</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -3737,12 +3573,12 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>2013-07-17</t>
+          <t>2012-01-27</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Traçabilité - Christian Etchebest - Connaître l'origine de la viande en restauration</t>
+          <t>Nouvelle pub - 3 produits laitiers par jour - 20s</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -3752,14 +3588,15 @@
       </c>
       <c r="I104" s="7" t="inlineStr"/>
       <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="8" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>XYZ Generation</t>
+          <t>Pierre Chomet Foie Gras poêlé</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -3777,12 +3614,12 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>XYZ Generation - Mathieu, duck breeder and fattener from generation to generation</t>
+          <t>Le Foie Gras en Reels - E4 - Pinchos de Foie Gras poêlé par Pierre Chomet</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -3792,19 +3629,20 @@
       </c>
       <c r="I105" s="7" t="inlineStr"/>
       <c r="J105" s="7" t="inlineStr"/>
+      <c r="K105" s="7" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="8" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Air France Découvrez l'élevag</t>
+          <t>Pub TV</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -3813,16 +3651,16 @@
         </is>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>2013-12-04</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras prend les airs avec Air France</t>
+          <t>Pub TV - Les Produits Laitiers Manga - Environnement</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -3832,14 +3670,15 @@
       </c>
       <c r="I106" s="7" t="inlineStr"/>
       <c r="J106" s="7" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="8" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Alisson Apprentie Boucher</t>
+          <t>Recette Cuisine Viande</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -3853,16 +3692,16 @@
         </is>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2013-07-05</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Alisson Apprentie Boucher - Pourquoi veut-elle être boucher?</t>
+          <t>Recette Cuisine Viande - Cœur de veau farci et carottes au cumin</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -3872,14 +3711,15 @@
       </c>
       <c r="I107" s="7" t="inlineStr"/>
       <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="8" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Amour Bœuf</t>
+          <t>Recette de Cuisine Viande</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -3893,16 +3733,16 @@
         </is>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Amour Bœuf - le carpaccio</t>
+          <t>Recette de Cuisine Viande - Rôti de viande chevaline</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -3912,19 +3752,20 @@
       </c>
       <c r="I108" s="7" t="inlineStr"/>
       <c r="J108" s="7" t="inlineStr"/>
+      <c r="K108" s="7" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="8" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>André Daguin</t>
+          <t>Spot radio</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
@@ -3933,16 +3774,16 @@
         </is>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Interview André Daguin "l'inventeur" du Magret par Jean-Claude Narcy</t>
+          <t>Spot radio - VOLAILLE FRANCAISE</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -3952,19 +3793,20 @@
       </c>
       <c r="I109" s="7" t="inlineStr"/>
       <c r="J109" s="7" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="8" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Anne du blog Panier de Saison</t>
+          <t>Stéphanie Sardain et Vincent</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -3973,16 +3815,16 @@
         </is>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Anne du blog Panier de Saison</t>
+          <t>Volaillissimes - Volaillers : rencontre avec Stéphanie Sardain et Vincent Dumontet (version courte)</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -3992,14 +3834,15 @@
       </c>
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="7" t="inlineStr"/>
+      <c r="K110" s="7" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="8" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Antoine Herth</t>
+          <t>Traçabilité</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -4013,16 +3856,16 @@
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2013-07-17</t>
         </is>
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Antoine Herth - Salon de l'agriculture 2014</t>
+          <t>Traçabilité - Christian Etchebest - Connaître l'origine de la viande en restauration</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -4032,19 +3875,20 @@
       </c>
       <c r="I111" s="7" t="inlineStr"/>
       <c r="J111" s="7" t="inlineStr"/>
+      <c r="K111" s="7" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Boris Tillot</t>
+          <t>XYZ Generation</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
@@ -4053,16 +3897,16 @@
         </is>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes -  Marché de gros : rencontre avec Boris Tillot (version courte)</t>
+          <t>XYZ Generation - Mathieu, duck breeder and fattener from generation to generation</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -4072,19 +3916,20 @@
       </c>
       <c r="I112" s="7" t="inlineStr"/>
       <c r="J112" s="7" t="inlineStr"/>
+      <c r="K112" s="7" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="8" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Boris Tillot Partez à la renc</t>
+          <t>Air France Découvrez l'élevag</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
@@ -4097,12 +3942,12 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2013-12-04</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes – Marché de gros : rencontre avec Boris Tillot</t>
+          <t>Le Foie Gras prend les airs avec Air France</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -4112,14 +3957,15 @@
       </c>
       <c r="I113" s="7" t="inlineStr"/>
       <c r="J113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="8" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Bruno Le Maire</t>
+          <t>Alisson Apprentie Boucher</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -4137,12 +3983,12 @@
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>Bruno Le Maire - Salon de l'agriculture 2014</t>
+          <t>Alisson Apprentie Boucher - Pourquoi veut-elle être boucher?</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -4152,19 +3998,20 @@
       </c>
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="7" t="inlineStr"/>
+      <c r="K114" s="7" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="8" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Challenge Foie Gras 2014</t>
+          <t>Amour Bœuf</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -4177,12 +4024,12 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>Challenge Foie Gras 2014 : le making-of !</t>
+          <t>Amour Bœuf - le carpaccio</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -4192,19 +4039,20 @@
       </c>
       <c r="I115" s="7" t="inlineStr"/>
       <c r="J115" s="7" t="inlineStr"/>
+      <c r="K115" s="7" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="8" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Changement climatique</t>
+          <t>André Daguin</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -4217,12 +4065,12 @@
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>2015-02-17</t>
+          <t>2017-11-10</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Changement climatique : les éleveurs s'adaptent</t>
+          <t>Interview André Daguin "l'inventeur" du Magret par Jean-Claude Narcy</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
@@ -4232,14 +4080,15 @@
       </c>
       <c r="I116" s="7" t="inlineStr"/>
       <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="8" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Charline Picon - Championne d</t>
+          <t>Anne du blog Panier de Saison</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4257,12 +4106,12 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>2015-08-21</t>
+          <t>2014-12-19</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Charline Picon - Championne du Monde RS:X 2014 - Planche à voile olympique</t>
+          <t>Entretien avec Anne du blog Panier de Saison</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
@@ -4272,14 +4121,15 @@
       </c>
       <c r="I117" s="7" t="inlineStr"/>
       <c r="J117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="8" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 01</t>
+          <t>Antoine Herth</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -4297,12 +4147,12 @@
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 01 - Qu'est-ce qu'un bon éleveur ?</t>
+          <t>Antoine Herth - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
@@ -4312,19 +4162,20 @@
       </c>
       <c r="I118" s="7" t="inlineStr"/>
       <c r="J118" s="7" t="inlineStr"/>
+      <c r="K118" s="7" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="8" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 02</t>
+          <t>Boris Tillot</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -4337,12 +4188,12 @@
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 02 - Qu'est-ce qu'un éleveur engraisseur ?</t>
+          <t>Volaillissimes -  Marché de gros : rencontre avec Boris Tillot (version courte)</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
@@ -4352,19 +4203,20 @@
       </c>
       <c r="I119" s="7" t="inlineStr"/>
       <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="8" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 03</t>
+          <t>Boris Tillot Partez à la renc</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -4377,12 +4229,12 @@
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 03 - Quels sont les atouts de l'élevage français ?</t>
+          <t>Volaillissimes – Marché de gros : rencontre avec Boris Tillot</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -4392,14 +4244,15 @@
       </c>
       <c r="I120" s="7" t="inlineStr"/>
       <c r="J120" s="7" t="inlineStr"/>
+      <c r="K120" s="7" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="8" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 04</t>
+          <t>Bruno Le Maire</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4417,12 +4270,12 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Claude Petitguyot 04 - Pourquoi acheter français ?</t>
+          <t>Bruno Le Maire - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
@@ -4432,14 +4285,15 @@
       </c>
       <c r="I121" s="7" t="inlineStr"/>
       <c r="J121" s="7" t="inlineStr"/>
+      <c r="K121" s="7" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="8" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Clotilde Jacoulot Découvrez l</t>
+          <t>Challenge Foie Gras 2014</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
@@ -4457,12 +4311,12 @@
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>2016-07-29</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Apéro gourmet avec le Foie Gras et le Magret par Clotilde Jacoulot</t>
+          <t>Challenge Foie Gras 2014 : le making-of !</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -4472,14 +4326,15 @@
       </c>
       <c r="I122" s="7" t="inlineStr"/>
       <c r="J122" s="7" t="inlineStr"/>
+      <c r="K122" s="7" t="inlineStr"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="8" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Comptine 01</t>
+          <t>Changement climatique</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4497,12 +4352,12 @@
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2015-02-17</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Comptine 01 - Gaston</t>
+          <t>Changement climatique : les éleveurs s'adaptent</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
@@ -4512,14 +4367,15 @@
       </c>
       <c r="I123" s="7" t="inlineStr"/>
       <c r="J123" s="7" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="8" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Comptine 02</t>
+          <t>Charline Picon - Championne d</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
@@ -4537,12 +4393,12 @@
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2015-08-21</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Comptine 02 - Le beau métier</t>
+          <t>Entretien avec Charline Picon - Championne du Monde RS:X 2014 - Planche à voile olympique</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
@@ -4552,14 +4408,15 @@
       </c>
       <c r="I124" s="7" t="inlineStr"/>
       <c r="J124" s="7" t="inlineStr"/>
+      <c r="K124" s="7" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="8" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Comptine 03</t>
+          <t>Claude Petitguyot 01</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4582,7 +4439,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Comptine 03 - Le rififi</t>
+          <t>Claude Petitguyot 01 - Qu'est-ce qu'un bon éleveur ?</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
@@ -4592,14 +4449,15 @@
       </c>
       <c r="I125" s="7" t="inlineStr"/>
       <c r="J125" s="7" t="inlineStr"/>
+      <c r="K125" s="7" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="8" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Comptine 04</t>
+          <t>Claude Petitguyot 02</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -4622,7 +4480,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>Comptine 04 - Marguerite</t>
+          <t>Claude Petitguyot 02 - Qu'est-ce qu'un éleveur engraisseur ?</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
@@ -4632,14 +4490,15 @@
       </c>
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="8" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Dorian du blog Mais Pourquoi</t>
+          <t>Claude Petitguyot 03</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -4657,12 +4516,12 @@
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>2014-12-08</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Dorian du blog Mais Pourquoi est-ce que je vous raconte ça?</t>
+          <t>Claude Petitguyot 03 - Quels sont les atouts de l'élevage français ?</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -4672,14 +4531,15 @@
       </c>
       <c r="I127" s="7" t="inlineStr"/>
       <c r="J127" s="7" t="inlineStr"/>
+      <c r="K127" s="7" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="8" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Découpe de tête de veau</t>
+          <t>Claude Petitguyot 04</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
@@ -4697,12 +4557,12 @@
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>2014-02-26</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>Découpe de tête de veau - Show boucher</t>
+          <t>Claude Petitguyot 04 - Pourquoi acheter français ?</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -4712,19 +4572,20 @@
       </c>
       <c r="I128" s="7" t="inlineStr"/>
       <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="8" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Edda du blog Un déjeuner de S</t>
+          <t>Clotilde Jacoulot Découvrez l</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
@@ -4737,12 +4598,12 @@
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>2014-12-15</t>
+          <t>2016-07-29</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Edda du blog Un déjeuner de Soleil</t>
+          <t>Apéro gourmet avec le Foie Gras et le Magret par Clotilde Jacoulot</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -4752,19 +4613,20 @@
       </c>
       <c r="I129" s="7" t="inlineStr"/>
       <c r="J129" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="8" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Emmanuel Coyaud</t>
+          <t>Comptine 01</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
@@ -4777,12 +4639,12 @@
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Industrie Agroalimentaire : rencontre avec Emmanuel Coyaud (version courte)</t>
+          <t>Comptine 01 - Gaston</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -4792,19 +4654,20 @@
       </c>
       <c r="I130" s="7" t="inlineStr"/>
       <c r="J130" s="7" t="inlineStr"/>
+      <c r="K130" s="7" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="8" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Emmanuel Coyaud Partez à la r</t>
+          <t>Comptine 02</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -4817,12 +4680,12 @@
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Industrie Agroalimentaire : rencontre avec Emmanuel Coyaud</t>
+          <t>Comptine 02 - Le beau métier</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -4832,19 +4695,20 @@
       </c>
       <c r="I131" s="7" t="inlineStr"/>
       <c r="J131" s="7" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="8" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>En vidéo</t>
+          <t>Comptine 03</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
@@ -4857,12 +4721,12 @@
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>2015-10-27</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>En vidéo : la filière Foie Gras engagée dans la démarche PalmiG Confiance</t>
+          <t>Comptine 03 - Le rififi</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -4872,14 +4736,15 @@
       </c>
       <c r="I132" s="7" t="inlineStr"/>
       <c r="J132" s="7" t="inlineStr"/>
+      <c r="K132" s="7" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="8" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Eric Andrieu</t>
+          <t>Comptine 04</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
@@ -4897,12 +4762,12 @@
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>Eric Andrieu - Salon de l'agriculture 2014</t>
+          <t>Comptine 04 - Marguerite</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
@@ -4912,19 +4777,20 @@
       </c>
       <c r="I133" s="7" t="inlineStr"/>
       <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="8" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Eric Birlouez</t>
+          <t>Dorian du blog Mais Pourquoi</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
@@ -4937,12 +4803,12 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>2017-02-21</t>
+          <t>2014-12-08</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>Cheese Day part. 1</t>
+          <t>Entretien avec Dorian du blog Mais Pourquoi est-ce que je vous raconte ça?</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -4952,19 +4818,20 @@
       </c>
       <c r="I134" s="7" t="inlineStr"/>
       <c r="J134" s="7" t="inlineStr"/>
+      <c r="K134" s="7" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="8" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Evénement</t>
+          <t>Découpe de tête de veau</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -4977,12 +4844,12 @@
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2014-02-26</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Evénement : à la découverte du Magret de canard</t>
+          <t>Découpe de tête de veau - Show boucher</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -4992,14 +4859,15 @@
       </c>
       <c r="I135" s="7" t="inlineStr"/>
       <c r="J135" s="7" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="8" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Expert d'élevage</t>
+          <t>Edda du blog Un déjeuner de S</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
@@ -5017,12 +4885,12 @@
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>2013-07-11</t>
+          <t>2014-12-15</t>
         </is>
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Expert d'élevage : les vaches nourries à l'herbe - production naturelle, économique, de qualité</t>
+          <t>Entretien avec Edda du blog Un déjeuner de Soleil</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
@@ -5032,19 +4900,20 @@
       </c>
       <c r="I136" s="7" t="inlineStr"/>
       <c r="J136" s="7" t="inlineStr"/>
+      <c r="K136" s="7" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="8" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Fabien</t>
+          <t>Emmanuel Coyaud</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
@@ -5057,12 +4926,12 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Fabien, boucher chevalin</t>
+          <t>Volaillissimes - Industrie Agroalimentaire : rencontre avec Emmanuel Coyaud (version courte)</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
@@ -5072,19 +4941,20 @@
       </c>
       <c r="I137" s="7" t="inlineStr"/>
       <c r="J137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="8" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Fabien Chevalier</t>
+          <t>Emmanuel Coyaud Partez à la r</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -5097,12 +4967,12 @@
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras : ambassadeur de la gastronomie française</t>
+          <t>Volaillissimes - Industrie Agroalimentaire : rencontre avec Emmanuel Coyaud</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
@@ -5112,19 +4982,20 @@
       </c>
       <c r="I138" s="7" t="inlineStr"/>
       <c r="J138" s="7" t="inlineStr"/>
+      <c r="K138" s="7" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="8" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Filière viande</t>
+          <t>En vidéo</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -5137,12 +5008,12 @@
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
+          <t>2015-10-27</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Filière viande : une source de valeurs pour la France?</t>
+          <t>En vidéo : la filière Foie Gras engagée dans la démarche PalmiG Confiance</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
@@ -5152,19 +5023,20 @@
       </c>
       <c r="I139" s="7" t="inlineStr"/>
       <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="8" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Florent De Maria</t>
+          <t>Eric Andrieu</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -5177,12 +5049,12 @@
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>Milk Moments</t>
+          <t>Eric Andrieu - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -5192,19 +5064,20 @@
       </c>
       <c r="I140" s="7" t="inlineStr"/>
       <c r="J140" s="7" t="inlineStr"/>
+      <c r="K140" s="7" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="8" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>Florian Boucherie</t>
+          <t>Eric Birlouez</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -5217,12 +5090,12 @@
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2017-02-21</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>Rencontres sur la route du Foie Gras – E1 : A la découverte de l'élevage</t>
+          <t>Cheese Day part. 1</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
@@ -5232,14 +5105,15 @@
       </c>
       <c r="I141" s="7" t="inlineStr"/>
       <c r="J141" s="7" t="inlineStr"/>
+      <c r="K141" s="7" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="8" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>Florian et tenter de le surpr</t>
+          <t>Evénement</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
@@ -5257,12 +5131,12 @@
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
+          <t>Evénement : à la découverte du Magret de canard</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
@@ -5272,19 +5146,20 @@
       </c>
       <c r="I142" s="7" t="inlineStr"/>
       <c r="J142" s="7" t="inlineStr"/>
+      <c r="K142" s="7" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="8" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>FlorianOnAir</t>
+          <t>Expert d'élevage</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
@@ -5297,12 +5172,12 @@
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2013-07-11</t>
         </is>
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Le Mois de la Volaille Française avec FlorianOnAir</t>
+          <t>Expert d'élevage : les vaches nourries à l'herbe - production naturelle, économique, de qualité</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
@@ -5312,19 +5187,20 @@
       </c>
       <c r="I143" s="7" t="inlineStr"/>
       <c r="J143" s="7" t="inlineStr"/>
+      <c r="K143" s="7" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="8" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras</t>
+          <t>Fabien</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -5337,12 +5213,12 @@
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>2015-03-09</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras : Um produto regional francês</t>
+          <t>Interview Métiers - Fabien, boucher chevalin</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
@@ -5352,14 +5228,15 @@
       </c>
       <c r="I144" s="7" t="inlineStr"/>
       <c r="J144" s="7" t="inlineStr"/>
+      <c r="K144" s="7" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="8" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras 2017</t>
+          <t>Fabien Chevalier</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
@@ -5377,12 +5254,12 @@
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>2017-11-02</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras 2017 :  la filière en ordre de marche pour le produit festif préféré des français !</t>
+          <t>Le Foie Gras : ambassadeur de la gastronomie française</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
@@ -5392,19 +5269,20 @@
       </c>
       <c r="I145" s="7" t="inlineStr"/>
       <c r="J145" s="7" t="inlineStr"/>
+      <c r="K145" s="7" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="8" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras et Magret</t>
+          <t>Filière viande</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
@@ -5417,12 +5295,12 @@
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>2014-11-14</t>
+          <t>2013-07-25</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras et Magret : les recettes de Frédéric Jaunault, Meilleur Ouvrier de France Primeur</t>
+          <t>Filière viande : une source de valeurs pour la France?</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
@@ -5432,19 +5310,20 @@
       </c>
       <c r="I146" s="7" t="inlineStr"/>
       <c r="J146" s="7" t="inlineStr"/>
+      <c r="K146" s="7" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="8" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels</t>
+          <t>Florent De Maria</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -5457,12 +5336,12 @@
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels - E3 – The Origins of Foie Gras, by Pierre Chomet!</t>
+          <t>Milk Moments</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -5472,14 +5351,15 @@
       </c>
       <c r="I147" s="7" t="inlineStr"/>
       <c r="J147" s="7" t="inlineStr"/>
+      <c r="K147" s="7" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="8" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels - E1</t>
+          <t>Florian Boucherie</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
@@ -5497,12 +5377,12 @@
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels - E1 - Understanding fattening... straight from the grocery store!</t>
+          <t>Rencontres sur la route du Foie Gras – E1 : A la découverte de l'élevage</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
@@ -5512,14 +5392,15 @@
       </c>
       <c r="I148" s="7" t="inlineStr"/>
       <c r="J148" s="7" t="inlineStr"/>
+      <c r="K148" s="7" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="8" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels - E2</t>
+          <t>Florian et tenter de le surpr</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
@@ -5537,12 +5418,12 @@
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras in Reels - E2 - Animal welfare and quality products from Pierre Chomet's restaurant</t>
+          <t>Rencontres sur la route du Foie Gras – E2 : En cuisine avec Matthias Marc et Pierre Chomet !</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
@@ -5552,19 +5433,20 @@
       </c>
       <c r="I149" s="7" t="inlineStr"/>
       <c r="J149" s="7" t="inlineStr"/>
+      <c r="K149" s="7" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="8" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>François Fillon</t>
+          <t>FlorianOnAir</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -5577,12 +5459,12 @@
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>François Fillon - Salon de l'agriculture 2014</t>
+          <t>Le Mois de la Volaille Française avec FlorianOnAir</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
@@ -5592,19 +5474,20 @@
       </c>
       <c r="I150" s="7" t="inlineStr"/>
       <c r="J150" s="7" t="inlineStr"/>
+      <c r="K150" s="7" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="8" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>Fromage - Le Monstre</t>
+          <t>Foie Gras</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -5617,12 +5500,12 @@
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2015-03-09</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>Fromage - Le Monstre - 30s</t>
+          <t>Foie Gras : Um produto regional francês</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
@@ -5632,19 +5515,20 @@
       </c>
       <c r="I151" s="7" t="inlineStr"/>
       <c r="J151" s="7" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="8" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>Fromage Tu penses que tu ne p</t>
+          <t>Foie Gras 2017</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
@@ -5657,12 +5541,12 @@
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.3 Brochettes Boeuf x Fromage</t>
+          <t>Foie Gras 2017 :  la filière en ordre de marche pour le produit festif préféré des français !</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
@@ -5672,19 +5556,20 @@
       </c>
       <c r="I152" s="7" t="inlineStr"/>
       <c r="J152" s="7" t="inlineStr"/>
+      <c r="K152" s="7" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="8" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>Fromages de France</t>
+          <t>Foie Gras et Magret</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
@@ -5697,12 +5582,12 @@
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2014-11-14</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>Fromages de France - Le plaisir est déjà dans les mots - 1995</t>
+          <t>Foie Gras et Magret : les recettes de Frédéric Jaunault, Meilleur Ouvrier de France Primeur</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
@@ -5712,19 +5597,20 @@
       </c>
       <c r="I153" s="7" t="inlineStr"/>
       <c r="J153" s="7" t="inlineStr"/>
+      <c r="K153" s="7" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="8" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>Frédéric</t>
+          <t>Foie Gras in Reels</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
@@ -5737,12 +5623,12 @@
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>2014-02-24</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Frédéric, éleveur de bovins</t>
+          <t>Foie Gras in Reels - E3 – The Origins of Foie Gras, by Pierre Chomet!</t>
         </is>
       </c>
       <c r="H154" s="10" t="inlineStr">
@@ -5752,19 +5638,20 @@
       </c>
       <c r="I154" s="7" t="inlineStr"/>
       <c r="J154" s="7" t="inlineStr"/>
+      <c r="K154" s="7" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="8" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>Frédéric Boulajeri</t>
+          <t>Foie Gras in Reels - E1</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
@@ -5777,12 +5664,12 @@
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri (version courte)</t>
+          <t>Foie Gras in Reels - E1 - Understanding fattening... straight from the grocery store!</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
@@ -5792,19 +5679,20 @@
       </c>
       <c r="I155" s="7" t="inlineStr"/>
       <c r="J155" s="7" t="inlineStr"/>
+      <c r="K155" s="7" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="8" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>Frédéric Boulajeri Partez à l</t>
+          <t>Foie Gras in Reels - E2</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
@@ -5817,12 +5705,12 @@
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri</t>
+          <t>Foie Gras in Reels - E2 - Animal welfare and quality products from Pierre Chomet's restaurant</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
@@ -5832,19 +5720,20 @@
       </c>
       <c r="I156" s="7" t="inlineStr"/>
       <c r="J156" s="7" t="inlineStr"/>
+      <c r="K156" s="7" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="8" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>Frédéric Jaunault Frédéric Ja</t>
+          <t>François Fillon</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -5857,12 +5746,12 @@
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>2016-07-29</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>Apéro gourmet avec le Foie Gras et le Magret par Frédéric Jaunault</t>
+          <t>François Fillon - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
@@ -5872,19 +5761,20 @@
       </c>
       <c r="I157" s="7" t="inlineStr"/>
       <c r="J157" s="7" t="inlineStr"/>
+      <c r="K157" s="7" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="8" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>Geneviève Bellet</t>
+          <t>Fromage - Le Monstre</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
@@ -5897,12 +5787,12 @@
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>2014-11-12</t>
+          <t>2011-12-28</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>Recettes autour du Foie Gras par Geneviève Bellet, Meilleur Ouvrier de France Primeur</t>
+          <t>Fromage - Le Monstre - 30s</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
@@ -5912,19 +5802,20 @@
       </c>
       <c r="I158" s="7" t="inlineStr"/>
       <c r="J158" s="7" t="inlineStr"/>
+      <c r="K158" s="7" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="8" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>Geoffroy Terrasson</t>
+          <t>Fromage Tu penses que tu ne p</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
@@ -5937,12 +5828,12 @@
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson (version courte)</t>
+          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.3 Brochettes Boeuf x Fromage</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
@@ -5952,19 +5843,20 @@
       </c>
       <c r="I159" s="7" t="inlineStr"/>
       <c r="J159" s="7" t="inlineStr"/>
+      <c r="K159" s="7" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="8" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>Geoffroy Terrasson Partez à l</t>
+          <t>Fromages de France</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -5977,12 +5869,12 @@
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson</t>
+          <t>Fromages de France - Le plaisir est déjà dans les mots - 1995</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
@@ -5992,19 +5884,20 @@
       </c>
       <c r="I160" s="7" t="inlineStr"/>
       <c r="J160" s="7" t="inlineStr"/>
+      <c r="K160" s="7" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="8" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Gino Catena Partez à la renco</t>
+          <t>Frédéric</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
@@ -6017,12 +5910,12 @@
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2014-02-24</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Marché de gros : rencontre avec Gino Catena</t>
+          <t>Interview Métiers - Frédéric, éleveur de bovins</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
@@ -6032,19 +5925,20 @@
       </c>
       <c r="I161" s="7" t="inlineStr"/>
       <c r="J161" s="7" t="inlineStr"/>
+      <c r="K161" s="7" t="inlineStr"/>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="8" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Frédéric Boulajeri</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
@@ -6057,12 +5951,12 @@
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Guillaume, chef boucher en grande surface</t>
+          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri (version courte)</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
@@ -6072,19 +5966,20 @@
       </c>
       <c r="I162" s="7" t="inlineStr"/>
       <c r="J162" s="7" t="inlineStr"/>
+      <c r="K162" s="7" t="inlineStr"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="8" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Guillaume Garot</t>
+          <t>Frédéric Boulajeri Partez à l</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
@@ -6097,12 +5992,12 @@
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>Guillaume Garot - Salon de l'agriculture 2014</t>
+          <t>Volaillissimes - Volailler : rencontre avec Frédéric Boulajeri</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
@@ -6112,19 +6007,20 @@
       </c>
       <c r="I163" s="7" t="inlineStr"/>
       <c r="J163" s="7" t="inlineStr"/>
+      <c r="K163" s="7" t="inlineStr"/>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="8" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>Guillaume Sanchez</t>
+          <t>Frédéric Jaunault Frédéric Ja</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -6137,12 +6033,12 @@
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2016-07-29</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode 3 (avec Guillaume Sanchez)</t>
+          <t>Apéro gourmet avec le Foie Gras et le Magret par Frédéric Jaunault</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
@@ -6152,19 +6048,20 @@
       </c>
       <c r="I164" s="7" t="inlineStr"/>
       <c r="J164" s="7" t="inlineStr"/>
+      <c r="K164" s="7" t="inlineStr"/>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="8" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>Hakim Jemili</t>
+          <t>Geneviève Bellet</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
@@ -6177,12 +6074,12 @@
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>2022-03-17</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
+          <t>Recettes autour du Foie Gras par Geneviève Bellet, Meilleur Ouvrier de France Primeur</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
@@ -6192,19 +6089,20 @@
       </c>
       <c r="I165" s="7" t="inlineStr"/>
       <c r="J165" s="7" t="inlineStr"/>
+      <c r="K165" s="7" t="inlineStr"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="8" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>Harlem Désir</t>
+          <t>Geoffroy Terrasson</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
@@ -6217,12 +6115,12 @@
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>Harlem Désir - Salon de l'agriculture 2014</t>
+          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson (version courte)</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
@@ -6232,19 +6130,20 @@
       </c>
       <c r="I166" s="7" t="inlineStr"/>
       <c r="J166" s="7" t="inlineStr"/>
+      <c r="K166" s="7" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="8" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>Hervé Morin</t>
+          <t>Geoffroy Terrasson Partez à l</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
@@ -6257,12 +6156,12 @@
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>Hervé Morin - Salon de l'agriculture 2014</t>
+          <t>Volaillissimes - Boulangerie-Snacking : rencontre avec Geoffroy Terrasson</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
@@ -6272,19 +6171,20 @@
       </c>
       <c r="I167" s="7" t="inlineStr"/>
       <c r="J167" s="7" t="inlineStr"/>
+      <c r="K167" s="7" t="inlineStr"/>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="8" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>Hervé Pillaud A l'occasion de</t>
+          <t>Gino Catena Partez à la renco</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -6297,12 +6197,12 @@
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>2016-01-05</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Hervé Pillaud</t>
+          <t>Volaillissimes - Marché de gros : rencontre avec Gino Catena</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
@@ -6312,14 +6212,15 @@
       </c>
       <c r="I168" s="7" t="inlineStr"/>
       <c r="J168" s="7" t="inlineStr"/>
+      <c r="K168" s="7" t="inlineStr"/>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="8" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>I L'OVIN</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -6337,12 +6238,12 @@
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>2014-02-22</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>I L'OVIN - Prends ton avenir en main, adopte l'Ovin</t>
+          <t>Interview Métiers - Guillaume, chef boucher en grande surface</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
@@ -6352,14 +6253,15 @@
       </c>
       <c r="I169" s="7" t="inlineStr"/>
       <c r="J169" s="7" t="inlineStr"/>
+      <c r="K169" s="7" t="inlineStr"/>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="8" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>Interview de Yoni Saada</t>
+          <t>Guillaume Garot</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
@@ -6377,12 +6279,12 @@
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>Interview de Yoni Saada - Magic tripes 2014</t>
+          <t>Guillaume Garot - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
@@ -6392,14 +6294,15 @@
       </c>
       <c r="I170" s="7" t="inlineStr"/>
       <c r="J170" s="7" t="inlineStr"/>
+      <c r="K170" s="7" t="inlineStr"/>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="8" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Jamy</t>
+          <t>Guillaume Sanchez</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
@@ -6417,12 +6320,12 @@
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>MEDINE EN CUISINE (avec Jamy)</t>
+          <t>CHAUD! - Épisode 3 (avec Guillaume Sanchez)</t>
         </is>
       </c>
       <c r="H171" s="10" t="inlineStr">
@@ -6432,14 +6335,15 @@
       </c>
       <c r="I171" s="7" t="inlineStr"/>
       <c r="J171" s="7" t="inlineStr"/>
+      <c r="K171" s="7" t="inlineStr"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="8" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>Jamy Du lait</t>
+          <t>Hakim Jemili</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
@@ -6457,12 +6361,12 @@
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2022-03-17</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>Les différents laits, présentés par Jamy</t>
+          <t>LE GOUTER DE MES REVES avec Hakim Jemili, Redouane Bougheraba et Pierre Chomet</t>
         </is>
       </c>
       <c r="H172" s="10" t="inlineStr">
@@ -6472,14 +6376,15 @@
       </c>
       <c r="I172" s="7" t="inlineStr"/>
       <c r="J172" s="7" t="inlineStr"/>
+      <c r="K172" s="7" t="inlineStr"/>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="8" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Jean-Benoît</t>
+          <t>Harlem Désir</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
@@ -6497,12 +6402,12 @@
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Jean-Benoit, commerçant en bestiaux</t>
+          <t>Harlem Désir - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H173" s="10" t="inlineStr">
@@ -6512,19 +6417,20 @@
       </c>
       <c r="I173" s="7" t="inlineStr"/>
       <c r="J173" s="7" t="inlineStr"/>
+      <c r="K173" s="7" t="inlineStr"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="8" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>Jean-Claude Narcy De</t>
+          <t>Hervé Morin</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
@@ -6537,12 +6443,12 @@
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>Interview André Daguin "l'inventeur" du Magret par Jean-Claude Narcy</t>
+          <t>Hervé Morin - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
@@ -6552,14 +6458,15 @@
       </c>
       <c r="I174" s="7" t="inlineStr"/>
       <c r="J174" s="7" t="inlineStr"/>
+      <c r="K174" s="7" t="inlineStr"/>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="8" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Jean-François Aucouturier</t>
+          <t>Hervé Pillaud A l'occasion de</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
@@ -6577,12 +6484,12 @@
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2016-01-05</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>Comment les contrats déployés répondent aux besoins des éleveurs, metteurs en marché et abatteurs ?</t>
+          <t>Entretien avec Hervé Pillaud</t>
         </is>
       </c>
       <c r="H175" s="10" t="inlineStr">
@@ -6592,14 +6499,15 @@
       </c>
       <c r="I175" s="7" t="inlineStr"/>
       <c r="J175" s="7" t="inlineStr"/>
+      <c r="K175" s="7" t="inlineStr"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="8" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>Jean-Louis PEYRAUD Un monde s</t>
+          <t>I L'OVIN</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
@@ -6617,12 +6525,12 @@
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2014-02-22</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 5 - Contribution de l’élevage a la biodiversité avec Jean-Louis PEYRAUD</t>
+          <t>I L'OVIN - Prends ton avenir en main, adopte l'Ovin</t>
         </is>
       </c>
       <c r="H176" s="10" t="inlineStr">
@@ -6632,14 +6540,15 @@
       </c>
       <c r="I176" s="7" t="inlineStr"/>
       <c r="J176" s="7" t="inlineStr"/>
+      <c r="K176" s="7" t="inlineStr"/>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="8" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>Jean-Paul</t>
+          <t>Interview de Yoni Saada</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
@@ -6657,12 +6566,12 @@
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2014-11-09</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Jean-Paul, éleveur de veaux</t>
+          <t>Interview de Yoni Saada - Magic tripes 2014</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
@@ -6672,14 +6581,15 @@
       </c>
       <c r="I177" s="7" t="inlineStr"/>
       <c r="J177" s="7" t="inlineStr"/>
+      <c r="K177" s="7" t="inlineStr"/>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="8" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>Jorick Dorignac</t>
+          <t>Jamy</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
@@ -6697,12 +6607,12 @@
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode 2 (avec Jorick Dorignac)</t>
+          <t>MEDINE EN CUISINE (avec Jamy)</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
@@ -6712,19 +6622,20 @@
       </c>
       <c r="I178" s="7" t="inlineStr"/>
       <c r="J178" s="7" t="inlineStr"/>
+      <c r="K178" s="7" t="inlineStr"/>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="8" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>Joy Sorman</t>
+          <t>Jamy Du lait</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
@@ -6737,12 +6648,12 @@
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>2013-05-17</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>Joy Sorman - Comme une bête</t>
+          <t>Les différents laits, présentés par Jamy</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
@@ -6752,14 +6663,15 @@
       </c>
       <c r="I179" s="7" t="inlineStr"/>
       <c r="J179" s="7" t="inlineStr"/>
+      <c r="K179" s="7" t="inlineStr"/>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="8" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 01</t>
+          <t>Jean-Benoît</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
@@ -6777,12 +6689,12 @@
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 01 - La salaison oui... mais de bœuf !</t>
+          <t>Interview Métiers - Jean-Benoit, commerçant en bestiaux</t>
         </is>
       </c>
       <c r="H180" s="10" t="inlineStr">
@@ -6792,19 +6704,20 @@
       </c>
       <c r="I180" s="7" t="inlineStr"/>
       <c r="J180" s="7" t="inlineStr"/>
+      <c r="K180" s="7" t="inlineStr"/>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="8" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 02</t>
+          <t>Jean-Claude Narcy De</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
@@ -6817,12 +6730,12 @@
       </c>
       <c r="F181" s="8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2017-11-10</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 02 - La passion en héritage !</t>
+          <t>Interview André Daguin "l'inventeur" du Magret par Jean-Claude Narcy</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
@@ -6832,14 +6745,15 @@
       </c>
       <c r="I181" s="7" t="inlineStr"/>
       <c r="J181" s="7" t="inlineStr"/>
+      <c r="K181" s="7" t="inlineStr"/>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="8" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B182" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 03</t>
+          <t>Jean-François Aucouturier</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
@@ -6857,12 +6771,12 @@
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 03 - Le bœuf tout beau, tout bio !</t>
+          <t>Comment les contrats déployés répondent aux besoins des éleveurs, metteurs en marché et abatteurs ?</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
@@ -6872,14 +6786,15 @@
       </c>
       <c r="I182" s="7" t="inlineStr"/>
       <c r="J182" s="7" t="inlineStr"/>
+      <c r="K182" s="7" t="inlineStr"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="8" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 05</t>
+          <t>Jean-Louis PEYRAUD Un monde s</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
@@ -6897,12 +6812,12 @@
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 05 - La qualité pour tous… La grande distribution engagée !</t>
+          <t>BIEN ÉLEVÉE ! Émission 5 - Contribution de l’élevage a la biodiversité avec Jean-Louis PEYRAUD</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
@@ -6912,14 +6827,15 @@
       </c>
       <c r="I183" s="7" t="inlineStr"/>
       <c r="J183" s="7" t="inlineStr"/>
+      <c r="K183" s="7" t="inlineStr"/>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="8" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 06</t>
+          <t>Jean-Paul</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
@@ -6937,12 +6853,12 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>L'Amour Bœuf - Épisode 06 - Du marché aux bestiaux à l’assiette, le parcours d’une famille engagée !</t>
+          <t>Interview Métiers - Jean-Paul, éleveur de veaux</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
@@ -6952,19 +6868,20 @@
       </c>
       <c r="I184" s="7" t="inlineStr"/>
       <c r="J184" s="7" t="inlineStr"/>
+      <c r="K184" s="7" t="inlineStr"/>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="8" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>L'amour est dans le pré</t>
+          <t>Jorick Dorignac</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
@@ -6977,12 +6894,12 @@
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>2014-02-22</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>L'amour est dans le pré - Frappez à la porte du berger.</t>
+          <t>CHAUD! - Épisode 2 (avec Jorick Dorignac)</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
@@ -6992,19 +6909,20 @@
       </c>
       <c r="I185" s="7" t="inlineStr"/>
       <c r="J185" s="7" t="inlineStr"/>
+      <c r="K185" s="7" t="inlineStr"/>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="8" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>L'emmental et les pâtes</t>
+          <t>Joy Sorman</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
@@ -7017,12 +6935,12 @@
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2013-05-17</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>L'emmental et les pâtes - 1987</t>
+          <t>Joy Sorman - Comme une bête</t>
         </is>
       </c>
       <c r="H186" s="10" t="inlineStr">
@@ -7032,14 +6950,15 @@
       </c>
       <c r="I186" s="7" t="inlineStr"/>
       <c r="J186" s="7" t="inlineStr"/>
+      <c r="K186" s="7" t="inlineStr"/>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="8" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>La chasse aux insectes</t>
+          <t>L'Amour Bœuf - Épisode 01</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
@@ -7057,12 +6976,12 @@
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>2014-02-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>La chasse aux insectes - Episode 02</t>
+          <t>L'Amour Bœuf - Épisode 01 - La salaison oui... mais de bœuf !</t>
         </is>
       </c>
       <c r="H187" s="10" t="inlineStr">
@@ -7072,14 +6991,15 @@
       </c>
       <c r="I187" s="7" t="inlineStr"/>
       <c r="J187" s="7" t="inlineStr"/>
+      <c r="K187" s="7" t="inlineStr"/>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="8" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>La ferme du futur</t>
+          <t>L'Amour Bœuf - Épisode 02</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
@@ -7097,12 +7017,12 @@
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>2014-02-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>La ferme du futur - Episode 04</t>
+          <t>L'Amour Bœuf - Épisode 02 - La passion en héritage !</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
@@ -7112,19 +7032,20 @@
       </c>
       <c r="I188" s="7" t="inlineStr"/>
       <c r="J188" s="7" t="inlineStr"/>
+      <c r="K188" s="7" t="inlineStr"/>
     </row>
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="8" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels-E2</t>
+          <t>L'Amour Bœuf - Épisode 03</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
@@ -7137,12 +7058,12 @@
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels-E2- Bien-être animal et produit de qualité en direct du resto de Pierre Chomet</t>
+          <t>L'Amour Bœuf - Épisode 03 - Le bœuf tout beau, tout bio !</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
@@ -7152,19 +7073,20 @@
       </c>
       <c r="I189" s="7" t="inlineStr"/>
       <c r="J189" s="7" t="inlineStr"/>
+      <c r="K189" s="7" t="inlineStr"/>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="8" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>Le Magret</t>
+          <t>L'Amour Bœuf - Épisode 05</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D190" s="9" t="inlineStr">
@@ -7177,12 +7099,12 @@
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>Le Magret : les qualités de la volaille et le caractère de la viande rouge !</t>
+          <t>L'Amour Bœuf - Épisode 05 - La qualité pour tous… La grande distribution engagée !</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
@@ -7192,14 +7114,15 @@
       </c>
       <c r="I190" s="7" t="inlineStr"/>
       <c r="J190" s="7" t="inlineStr"/>
+      <c r="K190" s="7" t="inlineStr"/>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="8" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>Les aventures de Quentin</t>
+          <t>L'Amour Bœuf - Épisode 06</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
@@ -7217,12 +7140,12 @@
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>Les aventures de Quentin - Episode 2</t>
+          <t>L'Amour Bœuf - Épisode 06 - Du marché aux bestiaux à l’assiette, le parcours d’une famille engagée !</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
@@ -7232,19 +7155,20 @@
       </c>
       <c r="I191" s="7" t="inlineStr"/>
       <c r="J191" s="7" t="inlineStr"/>
+      <c r="K191" s="7" t="inlineStr"/>
     </row>
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="8" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>LES JONES</t>
+          <t>L'amour est dans le pré</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
@@ -7257,12 +7181,12 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2014-02-22</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>LES JONES - BURGERS</t>
+          <t>L'amour est dans le pré - Frappez à la porte du berger.</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
@@ -7272,19 +7196,20 @@
       </c>
       <c r="I192" s="7" t="inlineStr"/>
       <c r="J192" s="7" t="inlineStr"/>
+      <c r="K192" s="7" t="inlineStr"/>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="8" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>Lionel</t>
+          <t>L'emmental et les pâtes</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
@@ -7297,12 +7222,12 @@
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Lionel, éleveur d'ovins</t>
+          <t>L'emmental et les pâtes - 1987</t>
         </is>
       </c>
       <c r="H193" s="10" t="inlineStr">
@@ -7312,14 +7237,15 @@
       </c>
       <c r="I193" s="7" t="inlineStr"/>
       <c r="J193" s="7" t="inlineStr"/>
+      <c r="K193" s="7" t="inlineStr"/>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="8" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B194" s="9" t="inlineStr">
         <is>
-          <t>Loïc ce qui fait</t>
+          <t>La chasse aux insectes</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
@@ -7337,12 +7263,12 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2014-02-25</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
+          <t>La chasse aux insectes - Episode 02</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
@@ -7352,14 +7278,15 @@
       </c>
       <c r="I194" s="7" t="inlineStr"/>
       <c r="J194" s="7" t="inlineStr"/>
+      <c r="K194" s="7" t="inlineStr"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="8" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - Épisode 04</t>
+          <t>La ferme du futur</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
@@ -7377,12 +7304,12 @@
       </c>
       <c r="F195" s="8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2014-02-27</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - Épisode 04 - Du pré à la cantine : le bœuf français en cuisine collective !</t>
+          <t>La ferme du futur - Episode 04</t>
         </is>
       </c>
       <c r="H195" s="10" t="inlineStr">
@@ -7392,19 +7319,20 @@
       </c>
       <c r="I195" s="7" t="inlineStr"/>
       <c r="J195" s="7" t="inlineStr"/>
+      <c r="K195" s="7" t="inlineStr"/>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="8" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - Épisode 07</t>
+          <t>Le Foie Gras en Reels-E2</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
@@ -7417,12 +7345,12 @@
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
+          <t>Le Foie Gras en Reels-E2- Bien-être animal et produit de qualité en direct du resto de Pierre Chomet</t>
         </is>
       </c>
       <c r="H196" s="10" t="inlineStr">
@@ -7432,19 +7360,20 @@
       </c>
       <c r="I196" s="7" t="inlineStr"/>
       <c r="J196" s="7" t="inlineStr"/>
+      <c r="K196" s="7" t="inlineStr"/>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="8" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>Marine VAN SIMMERTIER En Fran</t>
+          <t>Le Magret</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
@@ -7457,12 +7386,12 @@
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 1 - Élevage herbager à taille humaine avec Marine VAN SIMMERTIER</t>
+          <t>Le Magret : les qualités de la volaille et le caractère de la viande rouge !</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
@@ -7472,14 +7401,15 @@
       </c>
       <c r="I197" s="7" t="inlineStr"/>
       <c r="J197" s="7" t="inlineStr"/>
+      <c r="K197" s="7" t="inlineStr"/>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="8" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>Maryvonne LAGARONNE En France</t>
+          <t>Les aventures de Quentin</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
@@ -7497,12 +7427,12 @@
       </c>
       <c r="F198" s="8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 3 - Élevage durable avec Maryvonne LAGARONNE</t>
+          <t>Les aventures de Quentin - Episode 2</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
@@ -7512,14 +7442,15 @@
       </c>
       <c r="I198" s="7" t="inlineStr"/>
       <c r="J198" s="7" t="inlineStr"/>
+      <c r="K198" s="7" t="inlineStr"/>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="8" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>Mehdi Maïzi et avec la partic</t>
+          <t>LES JONES</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
@@ -7537,12 +7468,12 @@
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>QUIZZ’IN AVEC MEHDI MAÏZI, SOSO MANESS, KAMETO, BIG COLOMBIEN ET YANNOU JR</t>
+          <t>LES JONES - BURGERS</t>
         </is>
       </c>
       <c r="H199" s="10" t="inlineStr">
@@ -7552,19 +7483,20 @@
       </c>
       <c r="I199" s="7" t="inlineStr"/>
       <c r="J199" s="7" t="inlineStr"/>
+      <c r="K199" s="7" t="inlineStr"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="8" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>Michel Fruchet</t>
+          <t>Lionel</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
@@ -7577,12 +7509,12 @@
       </c>
       <c r="F200" s="8" t="inlineStr">
         <is>
-          <t>2019-10-28</t>
+          <t>2014-05-26</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>Michel Fruchet : annonce du lancement des logos origine France</t>
+          <t>Interview Métiers - Lionel, éleveur d'ovins</t>
         </is>
       </c>
       <c r="H200" s="10" t="inlineStr">
@@ -7592,14 +7524,15 @@
       </c>
       <c r="I200" s="7" t="inlineStr"/>
       <c r="J200" s="7" t="inlineStr"/>
+      <c r="K200" s="7" t="inlineStr"/>
     </row>
     <row r="201" ht="30" customHeight="1">
       <c r="A201" s="8" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>Michel Idiart</t>
+          <t>Loïc ce qui fait</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
@@ -7617,12 +7550,12 @@
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G201" s="9" t="inlineStr">
         <is>
-          <t>Les territoires peuvent-ils renforcer la souveraineté alimentaire via l’engraissement ?</t>
+          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
         </is>
       </c>
       <c r="H201" s="10" t="inlineStr">
@@ -7632,19 +7565,20 @@
       </c>
       <c r="I201" s="7" t="inlineStr"/>
       <c r="J201" s="7" t="inlineStr"/>
+      <c r="K201" s="7" t="inlineStr"/>
     </row>
     <row r="202" ht="30" customHeight="1">
       <c r="A202" s="8" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>Mister V diffusé le vendredi</t>
+          <t>L’Amour Bœuf - Épisode 04</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
@@ -7657,12 +7591,12 @@
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
+          <t>L’Amour Bœuf - Épisode 04 - Du pré à la cantine : le bœuf français en cuisine collective !</t>
         </is>
       </c>
       <c r="H202" s="10" t="inlineStr">
@@ -7672,19 +7606,20 @@
       </c>
       <c r="I202" s="7" t="inlineStr"/>
       <c r="J202" s="7" t="inlineStr"/>
+      <c r="K202" s="7" t="inlineStr"/>
     </row>
     <row r="203" ht="30" customHeight="1">
       <c r="A203" s="8" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>MISTER V Redécouvrez la pub T</t>
+          <t>L’Amour Bœuf - Épisode 07</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
@@ -7697,12 +7632,12 @@
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
+          <t>L’Amour Bœuf - Épisode 07 - Le burger des champions</t>
         </is>
       </c>
       <c r="H203" s="10" t="inlineStr">
@@ -7712,19 +7647,20 @@
       </c>
       <c r="I203" s="7" t="inlineStr"/>
       <c r="J203" s="7" t="inlineStr"/>
+      <c r="K203" s="7" t="inlineStr"/>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="8" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>Mister V Vous nous l'aviez de</t>
+          <t>Marine VAN SIMMERTIER En Fran</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
@@ -7737,12 +7673,12 @@
       </c>
       <c r="F204" s="8" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>Teaser Pub TV Les Produits Laitiers x Mister V</t>
+          <t>BIEN ÉLEVÉE ! Émission 1 - Élevage herbager à taille humaine avec Marine VAN SIMMERTIER</t>
         </is>
       </c>
       <c r="H204" s="10" t="inlineStr">
@@ -7752,14 +7688,15 @@
       </c>
       <c r="I204" s="7" t="inlineStr"/>
       <c r="J204" s="7" t="inlineStr"/>
+      <c r="K204" s="7" t="inlineStr"/>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" s="8" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>Nadia du blog Paprikas</t>
+          <t>Maryvonne LAGARONNE En France</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
@@ -7777,12 +7714,12 @@
       </c>
       <c r="F205" s="8" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Nadia du blog Paprikas.fr</t>
+          <t>BIEN ÉLEVÉE ! Émission 3 - Élevage durable avec Maryvonne LAGARONNE</t>
         </is>
       </c>
       <c r="H205" s="10" t="inlineStr">
@@ -7792,19 +7729,20 @@
       </c>
       <c r="I205" s="7" t="inlineStr"/>
       <c r="J205" s="7" t="inlineStr"/>
+      <c r="K205" s="7" t="inlineStr"/>
     </row>
     <row r="206" ht="30" customHeight="1">
       <c r="A206" s="8" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>Nathalie de Masterchef</t>
+          <t>Mehdi Maïzi et avec la partic</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
@@ -7817,12 +7755,12 @@
       </c>
       <c r="F206" s="8" t="inlineStr">
         <is>
-          <t>2013-12-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="G206" s="9" t="inlineStr">
         <is>
-          <t>Foie Gras à la gelée de pomelos et moka d'Ethiopie par Nathalie de Masterchef</t>
+          <t>QUIZZ’IN AVEC MEHDI MAÏZI, SOSO MANESS, KAMETO, BIG COLOMBIEN ET YANNOU JR</t>
         </is>
       </c>
       <c r="H206" s="10" t="inlineStr">
@@ -7832,19 +7770,20 @@
       </c>
       <c r="I206" s="7" t="inlineStr"/>
       <c r="J206" s="7" t="inlineStr"/>
+      <c r="K206" s="7" t="inlineStr"/>
     </row>
     <row r="207" ht="30" customHeight="1">
       <c r="A207" s="8" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>Nicolas Dupont-Aignan</t>
+          <t>Michel Fruchet</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
@@ -7857,12 +7796,12 @@
       </c>
       <c r="F207" s="8" t="inlineStr">
         <is>
-          <t>2014-03-10</t>
+          <t>2019-10-28</t>
         </is>
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>Nicolas Dupont-Aignan - Salon de l'agriculture 2014</t>
+          <t>Michel Fruchet : annonce du lancement des logos origine France</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
@@ -7872,19 +7811,20 @@
       </c>
       <c r="I207" s="7" t="inlineStr"/>
       <c r="J207" s="7" t="inlineStr"/>
+      <c r="K207" s="7" t="inlineStr"/>
     </row>
     <row r="208" ht="30" customHeight="1">
       <c r="A208" s="8" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>Oies et Canards</t>
+          <t>Michel Idiart</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D208" s="9" t="inlineStr">
@@ -7897,12 +7837,12 @@
       </c>
       <c r="F208" s="8" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G208" s="9" t="inlineStr">
         <is>
-          <t>Oies et Canards : des conditions d'élevage précises</t>
+          <t>Les territoires peuvent-ils renforcer la souveraineté alimentaire via l’engraissement ?</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
@@ -7912,19 +7852,20 @@
       </c>
       <c r="I208" s="7" t="inlineStr"/>
       <c r="J208" s="7" t="inlineStr"/>
+      <c r="K208" s="7" t="inlineStr"/>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="8" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Mister V diffusé le vendredi</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
@@ -7937,12 +7878,12 @@
       </c>
       <c r="F209" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Olivier, responsable qualité en entreprise de transformation</t>
+          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
         </is>
       </c>
       <c r="H209" s="10" t="inlineStr">
@@ -7952,14 +7893,15 @@
       </c>
       <c r="I209" s="7" t="inlineStr"/>
       <c r="J209" s="7" t="inlineStr"/>
+      <c r="K209" s="7" t="inlineStr"/>
     </row>
     <row r="210" ht="30" customHeight="1">
       <c r="A210" s="8" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>Paf paf paf le loup</t>
+          <t>MISTER V Redécouvrez la pub T</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
@@ -7977,12 +7919,12 @@
       </c>
       <c r="F210" s="8" t="inlineStr">
         <is>
-          <t>2011-04-14</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>Paf paf paf le loup - Pub TV 20 secondes</t>
+          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
@@ -7992,19 +7934,20 @@
       </c>
       <c r="I210" s="7" t="inlineStr"/>
       <c r="J210" s="7" t="inlineStr"/>
+      <c r="K210" s="7" t="inlineStr"/>
     </row>
     <row r="211" ht="30" customHeight="1">
       <c r="A211" s="8" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>Pascal</t>
+          <t>Mister V Vous nous l'aviez de</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
@@ -8017,12 +7960,12 @@
       </c>
       <c r="F211" s="8" t="inlineStr">
         <is>
-          <t>2014-02-24</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Pascal, artisan boucher</t>
+          <t>Teaser Pub TV Les Produits Laitiers x Mister V</t>
         </is>
       </c>
       <c r="H211" s="10" t="inlineStr">
@@ -8032,14 +7975,15 @@
       </c>
       <c r="I211" s="7" t="inlineStr"/>
       <c r="J211" s="7" t="inlineStr"/>
+      <c r="K211" s="7" t="inlineStr"/>
     </row>
     <row r="212" ht="30" customHeight="1">
       <c r="A212" s="8" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>Pascal Nowak</t>
+          <t>Nadia du blog Paprikas</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
@@ -8057,12 +8001,12 @@
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2014-12-01</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>Conditions de réussite de la mise en place d’un contrat entre un metteur en marché et un abatteur ?</t>
+          <t>Entretien avec Nadia du blog Paprikas.fr</t>
         </is>
       </c>
       <c r="H212" s="10" t="inlineStr">
@@ -8072,14 +8016,15 @@
       </c>
       <c r="I212" s="7" t="inlineStr"/>
       <c r="J212" s="7" t="inlineStr"/>
+      <c r="K212" s="7" t="inlineStr"/>
     </row>
     <row r="213" ht="30" customHeight="1">
       <c r="A213" s="8" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>Philippe Geneletti</t>
+          <t>Nathalie de Masterchef</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr">
@@ -8097,12 +8042,12 @@
       </c>
       <c r="F213" s="8" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2013-12-04</t>
         </is>
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>Nos Chefs nous manquent - Episode 4 : Philippe Geneletti</t>
+          <t>Foie Gras à la gelée de pomelos et moka d'Ethiopie par Nathalie de Masterchef</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
@@ -8112,14 +8057,15 @@
       </c>
       <c r="I213" s="7" t="inlineStr"/>
       <c r="J213" s="7" t="inlineStr"/>
+      <c r="K213" s="7" t="inlineStr"/>
     </row>
     <row r="214" ht="30" customHeight="1">
       <c r="A214" s="8" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>Philippe SELLIER L’herbe</t>
+          <t>Nicolas Dupont-Aignan</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
@@ -8137,12 +8083,12 @@
       </c>
       <c r="F214" s="8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2014-03-10</t>
         </is>
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 2 - Autonomie alimentaire avec Philippe SELLIER</t>
+          <t>Nicolas Dupont-Aignan - Salon de l'agriculture 2014</t>
         </is>
       </c>
       <c r="H214" s="10" t="inlineStr">
@@ -8152,19 +8098,20 @@
       </c>
       <c r="I214" s="7" t="inlineStr"/>
       <c r="J214" s="7" t="inlineStr"/>
+      <c r="K214" s="7" t="inlineStr"/>
     </row>
     <row r="215" ht="30" customHeight="1">
       <c r="A215" s="8" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>Philippine Jaillet</t>
+          <t>Oies et Canards</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
@@ -8177,12 +8124,12 @@
       </c>
       <c r="F215" s="8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2013-12-09</t>
         </is>
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode 5 (avec Philippine Jaillet)</t>
+          <t>Oies et Canards : des conditions d'élevage précises</t>
         </is>
       </c>
       <c r="H215" s="10" t="inlineStr">
@@ -8192,19 +8139,20 @@
       </c>
       <c r="I215" s="7" t="inlineStr"/>
       <c r="J215" s="7" t="inlineStr"/>
+      <c r="K215" s="7" t="inlineStr"/>
     </row>
     <row r="216" ht="30" customHeight="1">
       <c r="A216" s="8" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet et Marie</t>
+          <t>Olivier</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
@@ -8217,12 +8165,12 @@
       </c>
       <c r="F216" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels -E3 –Les différents types de Foie Gras par Pierre Chomet et Marie, productrice</t>
+          <t>Interview Métiers - Olivier, responsable qualité en entreprise de transformation</t>
         </is>
       </c>
       <c r="H216" s="10" t="inlineStr">
@@ -8232,19 +8180,20 @@
       </c>
       <c r="I216" s="7" t="inlineStr"/>
       <c r="J216" s="7" t="inlineStr"/>
+      <c r="K216" s="7" t="inlineStr"/>
     </row>
     <row r="217" ht="30" customHeight="1">
       <c r="A217" s="8" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet Foie Gras au to</t>
+          <t>Paf paf paf le loup</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
@@ -8257,12 +8206,12 @@
       </c>
       <c r="F217" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2011-04-14</t>
         </is>
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels - E3 - Toast de Foie Gras au torchon, par Pierre Chomet</t>
+          <t>Paf paf paf le loup - Pub TV 20 secondes</t>
         </is>
       </c>
       <c r="H217" s="10" t="inlineStr">
@@ -8272,19 +8221,20 @@
       </c>
       <c r="I217" s="7" t="inlineStr"/>
       <c r="J217" s="7" t="inlineStr"/>
+      <c r="K217" s="7" t="inlineStr"/>
     </row>
     <row r="218" ht="30" customHeight="1">
       <c r="A218" s="8" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet Pain toasté</t>
+          <t>Pascal</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
@@ -8297,12 +8247,12 @@
       </c>
       <c r="F218" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2014-02-24</t>
         </is>
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels - E3 - Recette originale à base de Foie Gras, par Pierre Chomet</t>
+          <t>Interview Métiers - Pascal, artisan boucher</t>
         </is>
       </c>
       <c r="H218" s="10" t="inlineStr">
@@ -8312,19 +8262,20 @@
       </c>
       <c r="I218" s="7" t="inlineStr"/>
       <c r="J218" s="7" t="inlineStr"/>
+      <c r="K218" s="7" t="inlineStr"/>
     </row>
     <row r="219" ht="30" customHeight="1">
       <c r="A219" s="8" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet Un foie gras cr</t>
+          <t>Pascal Nowak</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
@@ -8337,12 +8288,12 @@
       </c>
       <c r="F219" s="8" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels - E2 - Foie Gras poêlé et son mole de cacao préparé par Pierre Chomet</t>
+          <t>Conditions de réussite de la mise en place d’un contrat entre un metteur en marché et un abatteur ?</t>
         </is>
       </c>
       <c r="H219" s="10" t="inlineStr">
@@ -8352,14 +8303,15 @@
       </c>
       <c r="I219" s="7" t="inlineStr"/>
       <c r="J219" s="7" t="inlineStr"/>
+      <c r="K219" s="7" t="inlineStr"/>
     </row>
     <row r="220" ht="30" customHeight="1">
       <c r="A220" s="8" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>Pierre Chomet Un Foie Gras cr</t>
+          <t>Philippe Geneletti</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
@@ -8377,12 +8329,12 @@
       </c>
       <c r="F220" s="8" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras en Reels - E2 - Foie Gras pôelé et mole de cacao par Pierre Chomet</t>
+          <t>Nos Chefs nous manquent - Episode 4 : Philippe Geneletti</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
@@ -8392,19 +8344,20 @@
       </c>
       <c r="I220" s="7" t="inlineStr"/>
       <c r="J220" s="7" t="inlineStr"/>
+      <c r="K220" s="7" t="inlineStr"/>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="8" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>Pub Fromage</t>
+          <t>Philippe SELLIER L’herbe</t>
         </is>
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
@@ -8417,12 +8370,12 @@
       </c>
       <c r="F221" s="8" t="inlineStr">
         <is>
-          <t>2012-04-05</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>Pub Fromage : quel est le parti pris du choix musical ?</t>
+          <t>BIEN ÉLEVÉE ! Émission 2 - Autonomie alimentaire avec Philippe SELLIER</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
@@ -8432,14 +8385,15 @@
       </c>
       <c r="I221" s="7" t="inlineStr"/>
       <c r="J221" s="7" t="inlineStr"/>
+      <c r="K221" s="7" t="inlineStr"/>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="8" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>PUB TV</t>
+          <t>Philippine Jaillet</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
@@ -8457,12 +8411,12 @@
       </c>
       <c r="F222" s="8" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
+          <t>CHAUD! - Épisode 5 (avec Philippine Jaillet)</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
@@ -8472,19 +8426,20 @@
       </c>
       <c r="I222" s="7" t="inlineStr"/>
       <c r="J222" s="7" t="inlineStr"/>
+      <c r="K222" s="7" t="inlineStr"/>
     </row>
     <row r="223" ht="30" customHeight="1">
       <c r="A223" s="8" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>Pâtes Tu penses que tu ne peu</t>
+          <t>Pierre Chomet et Marie</t>
         </is>
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
@@ -8497,12 +8452,12 @@
       </c>
       <c r="F223" s="8" t="inlineStr">
         <is>
-          <t>2018-11-02</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.1 Poulet Crème x Pâtes</t>
+          <t>Le Foie Gras en Reels -E3 –Les différents types de Foie Gras par Pierre Chomet et Marie, productrice</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
@@ -8512,19 +8467,20 @@
       </c>
       <c r="I223" s="7" t="inlineStr"/>
       <c r="J223" s="7" t="inlineStr"/>
+      <c r="K223" s="7" t="inlineStr"/>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="8" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>Quentin Mauro</t>
+          <t>Pierre Chomet Foie Gras au to</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
@@ -8537,12 +8493,12 @@
       </c>
       <c r="F224" s="8" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>CHAUD! - Épisode 1 (avec Quentin Mauro)</t>
+          <t>Le Foie Gras en Reels - E3 - Toast de Foie Gras au torchon, par Pierre Chomet</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
@@ -8552,19 +8508,20 @@
       </c>
       <c r="I224" s="7" t="inlineStr"/>
       <c r="J224" s="7" t="inlineStr"/>
+      <c r="K224" s="7" t="inlineStr"/>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="8" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>Régénérez votre corps</t>
+          <t>Pierre Chomet Pain toasté</t>
         </is>
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>CNIEL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
@@ -8577,12 +8534,12 @@
       </c>
       <c r="F225" s="8" t="inlineStr">
         <is>
-          <t>2011-06-29</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>Régénérez votre corps - 2004</t>
+          <t>Le Foie Gras en Reels - E3 - Recette originale à base de Foie Gras, par Pierre Chomet</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
@@ -8592,19 +8549,20 @@
       </c>
       <c r="I225" s="7" t="inlineStr"/>
       <c r="J225" s="7" t="inlineStr"/>
+      <c r="K225" s="7" t="inlineStr"/>
     </row>
     <row r="226" ht="30" customHeight="1">
       <c r="A226" s="8" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>Safari à la ferme</t>
+          <t>Pierre Chomet Un foie gras cr</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
@@ -8617,12 +8575,12 @@
       </c>
       <c r="F226" s="8" t="inlineStr">
         <is>
-          <t>2014-02-25</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>Safari à la ferme - Episode 01</t>
+          <t>Le Foie Gras en Reels - E2 - Foie Gras poêlé et son mole de cacao préparé par Pierre Chomet</t>
         </is>
       </c>
       <c r="H226" s="10" t="inlineStr">
@@ -8632,19 +8590,20 @@
       </c>
       <c r="I226" s="7" t="inlineStr"/>
       <c r="J226" s="7" t="inlineStr"/>
+      <c r="K226" s="7" t="inlineStr"/>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="8" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>Salma du blog Cuisinons en co</t>
+          <t>Pierre Chomet Un Foie Gras cr</t>
         </is>
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
@@ -8657,12 +8616,12 @@
       </c>
       <c r="F227" s="8" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Salma du blog Cuisinons en couleurs</t>
+          <t>Le Foie Gras en Reels - E2 - Foie Gras pôelé et mole de cacao par Pierre Chomet</t>
         </is>
       </c>
       <c r="H227" s="10" t="inlineStr">
@@ -8672,19 +8631,20 @@
       </c>
       <c r="I227" s="7" t="inlineStr"/>
       <c r="J227" s="7" t="inlineStr"/>
+      <c r="K227" s="7" t="inlineStr"/>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="8" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>Secret de Cheffe en vidéo</t>
+          <t>Pub Fromage</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
@@ -8697,12 +8657,12 @@
       </c>
       <c r="F228" s="8" t="inlineStr">
         <is>
-          <t>2018-12-05</t>
+          <t>2012-04-05</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>Secret de Cheffe en vidéo : la recette festive du Magret de canard</t>
+          <t>Pub Fromage : quel est le parti pris du choix musical ?</t>
         </is>
       </c>
       <c r="H228" s="10" t="inlineStr">
@@ -8712,14 +8672,15 @@
       </c>
       <c r="I228" s="7" t="inlineStr"/>
       <c r="J228" s="7" t="inlineStr"/>
+      <c r="K228" s="7" t="inlineStr"/>
     </row>
     <row r="229" ht="30" customHeight="1">
       <c r="A229" s="8" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>Sido Cuisto</t>
+          <t>PUB TV</t>
         </is>
       </c>
       <c r="C229" s="8" t="inlineStr">
@@ -8737,12 +8698,12 @@
       </c>
       <c r="F229" s="8" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.5 pâtes au saumon amélioré (avec Sido Cuisto)</t>
+          <t>PUB TV - LES PRODUITS LAITIERS x MISTER V</t>
         </is>
       </c>
       <c r="H229" s="10" t="inlineStr">
@@ -8752,19 +8713,20 @@
       </c>
       <c r="I229" s="7" t="inlineStr"/>
       <c r="J229" s="7" t="inlineStr"/>
+      <c r="K229" s="7" t="inlineStr"/>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="8" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>Steeve Bellanger</t>
+          <t>Pâtes Tu penses que tu ne peu</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
@@ -8777,12 +8739,12 @@
       </c>
       <c r="F230" s="8" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restauration traditionnelle : rencontre avec Steeve Bellanger (version courte)</t>
+          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.1 Poulet Crème x Pâtes</t>
         </is>
       </c>
       <c r="H230" s="10" t="inlineStr">
@@ -8792,19 +8754,20 @@
       </c>
       <c r="I230" s="7" t="inlineStr"/>
       <c r="J230" s="7" t="inlineStr"/>
+      <c r="K230" s="7" t="inlineStr"/>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="8" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>Steeve Bellanger Partez à la</t>
+          <t>Quentin Mauro</t>
         </is>
       </c>
       <c r="C231" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
@@ -8817,12 +8780,12 @@
       </c>
       <c r="F231" s="8" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restauration traditionnelle : rencontre avec Steeve Bellanger</t>
+          <t>CHAUD! - Épisode 1 (avec Quentin Mauro)</t>
         </is>
       </c>
       <c r="H231" s="10" t="inlineStr">
@@ -8832,19 +8795,20 @@
       </c>
       <c r="I231" s="7" t="inlineStr"/>
       <c r="J231" s="7" t="inlineStr"/>
+      <c r="K231" s="7" t="inlineStr"/>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="8" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>Sylvie qui élève des canards</t>
+          <t>Régénérez votre corps</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
@@ -8857,12 +8821,12 @@
       </c>
       <c r="F232" s="8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2011-06-29</t>
         </is>
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>Le Foie Gras : le plein air comme ADN</t>
+          <t>Régénérez votre corps - 2004</t>
         </is>
       </c>
       <c r="H232" s="10" t="inlineStr">
@@ -8872,14 +8836,15 @@
       </c>
       <c r="I232" s="7" t="inlineStr"/>
       <c r="J232" s="7" t="inlineStr"/>
+      <c r="K232" s="7" t="inlineStr"/>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="8" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>Sébastien VALTEAU L’élevage a</t>
+          <t>Safari à la ferme</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
@@ -8897,12 +8862,12 @@
       </c>
       <c r="F233" s="8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2014-02-25</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>BIEN ÉLEVÉE ! Émission 4 - Impact de l’élevage sur le climat avec Sébastien VALTEAU</t>
+          <t>Safari à la ferme - Episode 01</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
@@ -8912,14 +8877,15 @@
       </c>
       <c r="I233" s="7" t="inlineStr"/>
       <c r="J233" s="7" t="inlineStr"/>
+      <c r="K233" s="7" t="inlineStr"/>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="8" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>Tiphaine du blog Gourmandiser</t>
+          <t>Salma du blog Cuisinons en co</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
@@ -8942,7 +8908,7 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>Entretien avec Tiphaine du blog Gourmandiseries</t>
+          <t>Entretien avec Salma du blog Cuisinons en couleurs</t>
         </is>
       </c>
       <c r="H234" s="10" t="inlineStr">
@@ -8952,19 +8918,20 @@
       </c>
       <c r="I234" s="7" t="inlineStr"/>
       <c r="J234" s="7" t="inlineStr"/>
+      <c r="K234" s="7" t="inlineStr"/>
     </row>
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="8" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>Trailer</t>
+          <t>Secret de Cheffe en vidéo</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
@@ -8977,12 +8944,12 @@
       </c>
       <c r="F235" s="8" t="inlineStr">
         <is>
-          <t>2015-02-25</t>
+          <t>2018-12-05</t>
         </is>
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>Trailer - L'Homme à la Spatule au Salon de l'Agriculture</t>
+          <t>Secret de Cheffe en vidéo : la recette festive du Magret de canard</t>
         </is>
       </c>
       <c r="H235" s="10" t="inlineStr">
@@ -8992,19 +8959,20 @@
       </c>
       <c r="I235" s="7" t="inlineStr"/>
       <c r="J235" s="7" t="inlineStr"/>
+      <c r="K235" s="7" t="inlineStr"/>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="8" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>Viande Bio</t>
+          <t>Sido Cuisto</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
@@ -9017,12 +8985,12 @@
       </c>
       <c r="F236" s="8" t="inlineStr">
         <is>
-          <t>2017-05-10</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
-          <t>Viande Bio : Comment sont élevés les animaux.</t>
+          <t>MYRIAM MET DU BEURRE DANS TES EPINARDS – Ep.5 pâtes au saumon amélioré (avec Sido Cuisto)</t>
         </is>
       </c>
       <c r="H236" s="10" t="inlineStr">
@@ -9032,19 +9000,20 @@
       </c>
       <c r="I236" s="7" t="inlineStr"/>
       <c r="J236" s="7" t="inlineStr"/>
+      <c r="K236" s="7" t="inlineStr"/>
     </row>
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="8" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>Viande Elevage Bio</t>
+          <t>Steeve Bellanger</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
@@ -9057,12 +9026,12 @@
       </c>
       <c r="F237" s="8" t="inlineStr">
         <is>
-          <t>2013-06-07</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>Viande Elevage Bio - Le respect des équilibres avant tout !</t>
+          <t>Volaillissimes - Restauration traditionnelle : rencontre avec Steeve Bellanger (version courte)</t>
         </is>
       </c>
       <c r="H237" s="10" t="inlineStr">
@@ -9072,14 +9041,15 @@
       </c>
       <c r="I237" s="7" t="inlineStr"/>
       <c r="J237" s="7" t="inlineStr"/>
+      <c r="K237" s="7" t="inlineStr"/>
     </row>
     <row r="238" ht="30" customHeight="1">
       <c r="A238" s="8" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>Vincent Kerdoncuff</t>
+          <t>Steeve Bellanger Partez à la</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
@@ -9097,12 +9067,12 @@
       </c>
       <c r="F238" s="8" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restauration collective : rencontre avec Vincent Kerdoncuff (version courte)</t>
+          <t>Volaillissimes - Restauration traditionnelle : rencontre avec Steeve Bellanger</t>
         </is>
       </c>
       <c r="H238" s="10" t="inlineStr">
@@ -9112,19 +9082,20 @@
       </c>
       <c r="I238" s="7" t="inlineStr"/>
       <c r="J238" s="7" t="inlineStr"/>
+      <c r="K238" s="7" t="inlineStr"/>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="8" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>Vincent Kerdoncuff Partez à l</t>
+          <t>Sylvie qui élève des canards</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>CIFOG</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
@@ -9137,12 +9108,12 @@
       </c>
       <c r="F239" s="8" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restauration collective : rencontre avec Vincent Kerdoncuff</t>
+          <t>Le Foie Gras : le plein air comme ADN</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
@@ -9152,19 +9123,20 @@
       </c>
       <c r="I239" s="7" t="inlineStr"/>
       <c r="J239" s="7" t="inlineStr"/>
+      <c r="K239" s="7" t="inlineStr"/>
     </row>
     <row r="240" ht="30" customHeight="1">
       <c r="A240" s="8" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>Vincent Simon</t>
+          <t>Sébastien VALTEAU L’élevage a</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
@@ -9177,12 +9149,12 @@
       </c>
       <c r="F240" s="8" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restaurateur : rencontre avec Vincent Simon (version courte)</t>
+          <t>BIEN ÉLEVÉE ! Émission 4 - Impact de l’élevage sur le climat avec Sébastien VALTEAU</t>
         </is>
       </c>
       <c r="H240" s="10" t="inlineStr">
@@ -9192,19 +9164,20 @@
       </c>
       <c r="I240" s="7" t="inlineStr"/>
       <c r="J240" s="7" t="inlineStr"/>
+      <c r="K240" s="7" t="inlineStr"/>
     </row>
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="8" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>Vincent Simon Partez à la ren</t>
+          <t>Tiphaine du blog Gourmandiser</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
@@ -9217,12 +9190,12 @@
       </c>
       <c r="F241" s="8" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2014-12-19</t>
         </is>
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>Volaillissimes - Restaurateur : rencontre avec Vincent Simon</t>
+          <t>Entretien avec Tiphaine du blog Gourmandiseries</t>
         </is>
       </c>
       <c r="H241" s="10" t="inlineStr">
@@ -9232,14 +9205,15 @@
       </c>
       <c r="I241" s="7" t="inlineStr"/>
       <c r="J241" s="7" t="inlineStr"/>
+      <c r="K241" s="7" t="inlineStr"/>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="8" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>Véronique</t>
+          <t>Trailer</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
@@ -9257,12 +9231,12 @@
       </c>
       <c r="F242" s="8" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
+          <t>2015-02-25</t>
         </is>
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Véronique, éleveuse de bovins</t>
+          <t>Trailer - L'Homme à la Spatule au Salon de l'Agriculture</t>
         </is>
       </c>
       <c r="H242" s="10" t="inlineStr">
@@ -9272,19 +9246,20 @@
       </c>
       <c r="I242" s="7" t="inlineStr"/>
       <c r="J242" s="7" t="inlineStr"/>
+      <c r="K242" s="7" t="inlineStr"/>
     </row>
     <row r="243" ht="30" customHeight="1">
       <c r="A243" s="8" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>WEB SÉRIE CULINAIRE</t>
+          <t>Viande Bio</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
@@ -9297,12 +9272,12 @@
       </c>
       <c r="F243" s="8" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>WEB SÉRIE CULINAIRE : Nos Chefs nous manquent</t>
+          <t>Viande Bio : Comment sont élevés les animaux.</t>
         </is>
       </c>
       <c r="H243" s="10" t="inlineStr">
@@ -9312,14 +9287,15 @@
       </c>
       <c r="I243" s="7" t="inlineStr"/>
       <c r="J243" s="7" t="inlineStr"/>
+      <c r="K243" s="7" t="inlineStr"/>
     </row>
     <row r="244" ht="30" customHeight="1">
       <c r="A244" s="8" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Viande Elevage Bio</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
@@ -9337,12 +9313,12 @@
       </c>
       <c r="F244" s="8" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
+          <t>2013-06-07</t>
         </is>
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>Interview Métiers - Xavier, éleveur d'équins</t>
+          <t>Viande Elevage Bio - Le respect des équilibres avant tout !</t>
         </is>
       </c>
       <c r="H244" s="10" t="inlineStr">
@@ -9352,19 +9328,20 @@
       </c>
       <c r="I244" s="7" t="inlineStr"/>
       <c r="J244" s="7" t="inlineStr"/>
+      <c r="K244" s="7" t="inlineStr"/>
     </row>
     <row r="245" ht="30" customHeight="1">
       <c r="A245" s="8" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>Yves Puget</t>
+          <t>Vincent Kerdoncuff</t>
         </is>
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>CIFOG</t>
+          <t>ANVOL</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
@@ -9377,12 +9354,12 @@
       </c>
       <c r="F245" s="8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>REPLAY CIFOG Webinaire mars 2026</t>
+          <t>Volaillissimes - Restauration collective : rencontre avec Vincent Kerdoncuff (version courte)</t>
         </is>
       </c>
       <c r="H245" s="10" t="inlineStr">
@@ -9392,232 +9369,523 @@
       </c>
       <c r="I245" s="7" t="inlineStr"/>
       <c r="J245" s="7" t="inlineStr"/>
+      <c r="K245" s="7" t="inlineStr"/>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="8" t="n">
+        <v>212</v>
+      </c>
+      <c r="B246" s="9" t="inlineStr">
+        <is>
+          <t>Vincent Kerdoncuff Partez à l</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="8" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>Volaillissimes - Restauration collective : rencontre avec Vincent Kerdoncuff</t>
+        </is>
+      </c>
+      <c r="H246" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I246" s="7" t="inlineStr"/>
+      <c r="J246" s="7" t="inlineStr"/>
+      <c r="K246" s="7" t="inlineStr"/>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>Vincent Simon</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>Volaillissimes - Restaurateur : rencontre avec Vincent Simon (version courte)</t>
+        </is>
+      </c>
+      <c r="H247" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I247" s="7" t="inlineStr"/>
+      <c r="J247" s="7" t="inlineStr"/>
+      <c r="K247" s="7" t="inlineStr"/>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>Vincent Simon Partez à la ren</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>Volaillissimes - Restaurateur : rencontre avec Vincent Simon</t>
+        </is>
+      </c>
+      <c r="H248" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I248" s="7" t="inlineStr"/>
+      <c r="J248" s="7" t="inlineStr"/>
+      <c r="K248" s="7" t="inlineStr"/>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>Véronique</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>Interview Métiers - Véronique, éleveuse de bovins</t>
+        </is>
+      </c>
+      <c r="H249" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I249" s="7" t="inlineStr"/>
+      <c r="J249" s="7" t="inlineStr"/>
+      <c r="K249" s="7" t="inlineStr"/>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="8" t="n">
+        <v>216</v>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
+        <is>
+          <t>WEB SÉRIE CULINAIRE</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E250" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="8" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>WEB SÉRIE CULINAIRE : Nos Chefs nous manquent</t>
+        </is>
+      </c>
+      <c r="H250" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I250" s="7" t="inlineStr"/>
+      <c r="J250" s="7" t="inlineStr"/>
+      <c r="K250" s="7" t="inlineStr"/>
+    </row>
+    <row r="251" ht="30" customHeight="1">
+      <c r="A251" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="B251" s="9" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>2014-02-20</t>
+        </is>
+      </c>
+      <c r="G251" s="9" t="inlineStr">
+        <is>
+          <t>Interview Métiers - Xavier, éleveur d'équins</t>
+        </is>
+      </c>
+      <c r="H251" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I251" s="7" t="inlineStr"/>
+      <c r="J251" s="7" t="inlineStr"/>
+      <c r="K251" s="7" t="inlineStr"/>
+    </row>
+    <row r="252" ht="30" customHeight="1">
+      <c r="A252" s="8" t="n">
+        <v>218</v>
+      </c>
+      <c r="B252" s="9" t="inlineStr">
+        <is>
+          <t>Yves Puget</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>motif dans le titre</t>
+        </is>
+      </c>
+      <c r="E252" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>REPLAY CIFOG Webinaire mars 2026</t>
+        </is>
+      </c>
+      <c r="H252" s="10" t="inlineStr">
+        <is>
+          <t>voir la video</t>
+        </is>
+      </c>
+      <c r="I252" s="7" t="inlineStr"/>
+      <c r="J252" s="7" t="inlineStr"/>
+      <c r="K252" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245 I246 I247 I248 I249 I250 I251 I252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"oui, c'est un createur,non, c'est un nom de serie ou de campagne,non, c'est une marque ou un label,non, c'est un media,je ne sais pas"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114 J115 J116 J117 J118 J119 J120 J121 J122 J123 J124 J125 J126 J127 J128 J129 J130 J131 J132 J133 J134 J135 J136 J137 J138 J139 J140 J141 J142 J143 J144 J145 J146 J147 J148 J149 J150 J151 J152 J153 J154 J155 J156 J157 J158 J159 J160 J161 J162 J163 J164 J165 J166 J167 J168 J169 J170 J171 J172 J173 J174 J175 J176 J177 J178 J179 J180 J181 J182 J183 J184 J185 J186 J187 J188 J189 J190 J191 J192 J193 J194 J195 J196 J197 J198 J199 J200 J201 J202 J203 J204 J205 J206 J207 J208 J209 J210 J211 J212 J213 J214 J215 J216 J217 J218 J219 J220 J221 J222 J223 J224 J225 J226 J227 J228 J229 J230 J231 J232 J233 J234 J235 J236 J237 J238 J239 J240 J241 J242 J243 J244 J245 J246 J247 J248 J249 J250 J251 J252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"createur de contenu (youtubeur, tiktokeur, instagrameur),chef ou restaurateur,eleveur ou agriculteur,personnalite de television ou de radio,sportif,autre,je ne sais pas"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cartographie/CREATEURS_NOMMES_PAR_LES_LOBBIES.xlsx
+++ b/cartographie/CREATEURS_NOMMES_PAR_LES_LOBBIES.xlsx
@@ -758,9 +758,22 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Hakim Jemili et Redouane Bougheraba sont des humoristes. Ils ont des comptes Instagram &gt; Hakim Jemili : www.instagram.com/hakimjemili/ (937k followers) 
+Redouane Bougheraba : www.instagram.com/redouanebougheraba/ (1,4M followers) - du coup: pas des 'influenceurs' au sens classique du terme, mais des humoristes très suivis payés par les produits laitiers. Toujours intéressant je suppose. Est-ce ce serait nécéssaire de redéfinir ce que signifie 'influenceur' dans notre projet, ou de créer des catégories connexes? Pierre Chomet est juste un chef</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -840,9 +853,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>createur de contenu (youtubeur</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>&gt; @MorganVS (1,34M subscriver)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -881,9 +906,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>L'Amour Bœuf est le nom d'une série sur le chaîne Aimez la viande, déjà identifiée je crois</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="n">
@@ -923,8 +960,16 @@
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>C'est juste le titre de la vidéo, et les produits tripiers sont une catégorie de produits sur laquelle le lobby travaille (aussi sur la chaîne Aimez la viande)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -964,8 +1009,16 @@
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>C'est le nom d'un label de viande créé par le lobby</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="n">
@@ -1005,7 +1058,11 @@
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
       <c r="K41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
@@ -1046,8 +1103,16 @@
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Attention, c'est un prénom courant</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="n">
@@ -1087,8 +1152,16 @@
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Sûrement le nom d'un boutique. On s'en fiche</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -1210,8 +1283,16 @@
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr"/>
-      <c r="K46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>C'est juste comme ça qu'on appelle une équipe en cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="4" t="n">
@@ -1251,8 +1332,16 @@
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>C'est le nom d'un évènement important dans l'agriculture</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="4" t="n">
@@ -1292,8 +1381,16 @@
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>je crois que c'est le prénom de la manageuse de l'équipe qui a créé la vidéo. La vidéo fait partie d'une série déjà identifiée 'Les Copains au Lait' de Mister V</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="4" t="n">
@@ -1333,8 +1430,16 @@
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
-      <c r="K49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>"Découvrez la nouvelle campagne "Les Produits Laitiers" dans l'univers manga avec la voix de Brigitte Lecordier, célèbre voix de Son Goku dans Dragon Ball." &gt;&gt; Dans la description. Je ne comprends pas pourquoi les outils que tu as créé ne donne pas la partie intéressante de la description en entier pour permettre à la validation humaine de vérifier plus facilement sans avoir à cliquer sur le lien</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -1374,8 +1479,16 @@
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr"/>
-      <c r="K50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Découvrez les métiers des professionnels de la filière élevage et viande avec Bertrand, chef cuisinier en restauration scolaire." &gt; Vraiment, ça faciliterait la tâche du vérificateur humain d'avoir toute la phrase importante dans le fichier de vérification. Une autre idée qui me vient: as-tu déjà penser à une méthode pour éviter de soumettre aux vérificateurs humains les mêmes contenus plusieurs fois?</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="4" t="n">
@@ -1415,8 +1528,16 @@
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>C'est une appellation classique, pas un nom propre</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -1456,8 +1577,16 @@
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-      <c r="K52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Partez à la rencontre des professionnels qui ont dit « Oui à la Volaille Française ! ». Dans cet épisode, retrouvez Gino Catena, directeur général d'AVIGROS (grossiste en volailles de chair à Rungis)."</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="4" t="n">
@@ -1497,8 +1626,16 @@
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>C'est le nom d'une région. Je ne comprends pas pourquoi ça atterit là :/</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -1538,8 +1675,16 @@
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
-      <c r="K54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Antonjo, Eftidaï, Rabah, Alexandre et Kelly sont partis de la ferme… pour finir face aux chefs Guillaume Sanchez, Jorick Dorignac, Philippine Jaillet et Jeffrey Cagnes, au Salon de l’Agriculture, avec du très lourd dans les assiettes et un peu de pression dans les casseroles."</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="4" t="n">
@@ -1579,8 +1724,16 @@
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
-      <c r="K55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Cette fois, c'est à Voiron que le foodtruck 𝗔𝗶𝗺𝗲𝘇 𝗹𝗮 𝘃𝗶𝗮𝗻𝗱𝗲 𝗠𝗮𝗻𝗴𝗲𝘇-𝗲𝗻 𝗺𝗶𝗲𝘂𝘅 marque un arrêt pour le Tour de France 2026. On y retrouve le coureur paracycliste Romain Gioux accompagné de Laura Martinez, diététicienne-nutritionniste, pour un échange sur la nutrition sportive."</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -1620,8 +1773,20 @@
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Interview de Marine Le Pen, Présidente du Front national et Députée européenne.
+LaViandeTV interroge Marine Le Pen sur : 
+la démarche Viandes de France ;
+la mention de l'origine sur les plats préparés à base de viande et
+le poids de la filière élevage dans l'économie française."</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="4" t="n">
@@ -1661,8 +1826,16 @@
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Partez à la rencontre des professionnels qui ont dit « Oui à la Volaille Française ! ». Dans cet épisode, retrouvez Geoffroy Terrasson, artisan-boulanger à Lyon, qui nous explique pourquoi il a fait le choix de la Volaille Française pour sa Boulangerie Maison Terrasson."</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -1743,8 +1916,16 @@
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-      <c r="K59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>c'est juste un mot. Description: "Depuis 2019 INTERBEV déploie sa campagne de communication collective "Aimez la viande Mangez-en mieux", adossée à sa démarche de responsabilité sociétale. Avec la signature "Naturellement Flexitariens", l’interprofession a réaffirmé que l’homme était un omnivore, éclairé et attentif à l’origine de son alimentation."</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="4" t="n">
@@ -1784,8 +1965,17 @@
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>C'est juste le prénom d'un éleveur. Description: "L’herbe, c’est environ 78 % de l’alimentation des vaches.
+L’élevage bio de Philippe et Marie-Claire dans le bocage normand permet une biodiversité bien développée et de nourrir majoritairement leurs vaches avec de l’herbe et du foin issus de leur exploitation."</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="4" t="n">
@@ -1825,8 +2015,16 @@
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
-      <c r="K61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>C'est un évènement sportif. Description: "Cette fois, c'est à Voiron que le foodtruck 𝗔𝗶𝗺𝗲𝘇 𝗹𝗮 𝘃𝗶𝗮𝗻𝗱𝗲 𝗠𝗮𝗻𝗴𝗲𝘇-𝗲𝗻 𝗺𝗶𝗲𝘂𝘅 marque un arrêt pour le Tour de France 2026."</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -1866,8 +2064,16 @@
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
-      <c r="K62" s="7" t="inlineStr"/>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Je ne sais pas. Ce n'est pas en description. Probablement irrelevant.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="4" t="n">
@@ -1907,8 +2113,16 @@
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Forte des souvenirs de son enfance, Anne partage à ses lecteurs des recettes généreuses et faciles à réaliser. Passionnée de photo culinaire, son blog se dévore des yeux et invite à cuisiner, comme elle, pour inviter au dialogue."</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="4" t="n">
@@ -1948,8 +2162,17 @@
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Pour Benjamin, l’alimentation est un outil. Elle lui permet de garder le contrôle sur son physique, maîtriser son énergie et être plus performant. Pourtant ça n’a pas toujours été comme ça. Petit, il n’arrivait pas à se canaliser et était en surpoids. Alors en Bac professionnel électrotechnique, il se prend de passion pour la musculation. Il rêve d’en faire son métier mais pour lui, pour son entourage, impossible qu’il devienne coach. 
+Avec sa détermination, Benjamin leur a prouvé le contraire."</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="4" t="n">
@@ -1989,8 +2212,16 @@
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je ne sais pas. Il n'y a rien en description, mais ça ressemble à un évènement de greenwashing </t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="4" t="n">
@@ -2030,8 +2261,17 @@
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Trois invités apportent leur éclairage dans le débat « C'est pas tranché » :
+Blandine Vié, journaliste culinaire, auteur et créatrice du web magazine "Gretagarbure"  - http://gretagarbure.com …"</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="4" t="n">
@@ -2071,8 +2311,16 @@
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Je ne sais pas. Pas dans la description. Je ne sais pas d'où ça vient, mais probablement le nom d'une charcuterie.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2112,8 +2360,16 @@
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr"/>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Entretien avec Charline Picon - Championne du Monde RS:X 2014 - Planche à voile olympique"</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="4" t="n">
@@ -2153,8 +2409,16 @@
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Doublon; Description: "Forte des souvenirs de son enfance, Anne partage à ses lecteurs des recettes généreuses et faciles à réaliser. Passionnée de photo culinaire, son blog se dévore des yeux et invite à cuisiner, comme elle, pour inviter au dialogue."</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -2194,8 +2458,16 @@
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
-      <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Description: "À l'occasion du Tour de France 2026, l'ancien coureur cycliste Fabien Patanchon et la diététicienne-nutritionniste Patricia Poignet se sont retrouvés à Bordeaux, au foodtruck 𝗔𝗶𝗺𝗲𝘇 𝗹𝗮 𝘃𝗶𝗮𝗻𝗱𝗲 𝗠𝗮𝗻𝗴𝗲𝘇-𝗲𝗻 𝗺𝗶𝗲𝘂𝘅, pour échanger sur l'évolution de la nutrition dans le domaine du sport."</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="4" t="n">
@@ -2235,8 +2507,16 @@
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
-      <c r="J71" s="7" t="inlineStr"/>
-      <c r="K71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Pierre et Matthias passent en cuisine pour sublimer le Foie Gras produit par Florian et tenter de le surprendre avec des recettes faciles et originales !"</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -2276,8 +2556,16 @@
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>Probablement juste le nom d'une entreprise</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="4" t="n">
@@ -2399,7 +2687,11 @@
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
       <c r="K75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
@@ -2440,8 +2732,16 @@
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>"Mehdi Maïzi, né le 10 juillet 1986 à Aïn Taya en Algérie, est un journaliste musical et écrivain algéro-français spécialisé dans le rap."</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="4" t="n">
@@ -2481,8 +2781,16 @@
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-      <c r="K77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Déjà mentionné plus haut</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="4" t="n">
@@ -2522,8 +2830,16 @@
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-      <c r="K78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Découvrez le second épisode d'une série autour des fromages AOP, présentée par Morgan Niquet, qui découvre aujourd'hui les fromages à pâte pressée cuite. Dans cet épisode Morgan part à la rencontre de Romuald Fassenet, chef, Meilleur Ouvrier de France, dans le Jura."</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="4" t="n">
@@ -2563,8 +2879,16 @@
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>Je ne sais pas, on s'en fiche</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -2604,8 +2928,20 @@
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr"/>
-      <c r="J80" s="7" t="inlineStr"/>
-      <c r="K80" s="7" t="inlineStr"/>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>createur de contenu (youtubeur</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Vous nous l'aviez demandée, vous l'attendiez, et bien voici la pub Produits Laitiers avec Mister V !
+...
+Euh mouais... par contre on va en refaire une autre pour la télé...
+&gt; @TheoJuice a 65,9k subscribers
+Merci à Mister V et Theo Juice !"</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="4" t="n">
@@ -2726,8 +3062,16 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
       <c r="K83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
@@ -2767,7 +3111,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J84" s="7" t="inlineStr"/>
       <c r="K84" s="7" t="inlineStr"/>
     </row>
@@ -2808,7 +3156,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr"/>
       <c r="K85" s="7" t="inlineStr"/>
     </row>
@@ -2849,9 +3201,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr"/>
-      <c r="J86" s="7" t="inlineStr"/>
-      <c r="K86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>C'est juste l'acronyme de Made In Viande</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -2890,7 +3254,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr"/>
       <c r="K87" s="7" t="inlineStr"/>
     </row>
@@ -2931,8 +3299,16 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
       <c r="K88" s="7" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
@@ -2972,7 +3348,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J89" s="7" t="inlineStr"/>
       <c r="K89" s="7" t="inlineStr"/>
     </row>
@@ -3013,7 +3393,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J90" s="7" t="inlineStr"/>
       <c r="K90" s="7" t="inlineStr"/>
     </row>
@@ -3054,7 +3438,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J91" s="7" t="inlineStr"/>
       <c r="K91" s="7" t="inlineStr"/>
     </row>
@@ -3095,7 +3483,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr"/>
       <c r="K92" s="7" t="inlineStr"/>
     </row>
@@ -3136,7 +3528,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J93" s="7" t="inlineStr"/>
       <c r="K93" s="7" t="inlineStr"/>
     </row>
@@ -3177,7 +3573,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr"/>
       <c r="K94" s="7" t="inlineStr"/>
     </row>
@@ -3219,8 +3619,18 @@
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="7" t="inlineStr"/>
-      <c r="K95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Et vous, c’est quoi votre Milk Moment ?
+Film de la campagne de promotion collective du lait co-financée par la Commission Européenne.
+Musique originale par Grand Voyage (Florent De Maria, Jérémy Villecourt, Pierre Sendrané)."</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="8" t="n">
@@ -3260,7 +3670,11 @@
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
       <c r="K96" s="7" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
@@ -3300,9 +3714,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
-      <c r="K97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>createur de contenu (youtubeur</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>&gt; @mistervofficial (6,53M Subscribers)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="8" t="n">
@@ -3341,9 +3767,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="7" t="inlineStr"/>
-      <c r="K98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>createur de contenu (youtubeur</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>&gt; @mistervofficial (6,53M Subscribers)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -3383,8 +3821,16 @@
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Nathalie, finaliste de Masterchef 2011, présente sa recette autour du Foie Gras et du Magret : Magret de canard et son Foie Gras poêlé à l'émulsion de bière brune."</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="8" t="n">
@@ -3423,7 +3869,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J100" s="7" t="inlineStr"/>
       <c r="K100" s="7" t="inlineStr"/>
     </row>
@@ -3464,7 +3914,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J101" s="7" t="inlineStr"/>
       <c r="K101" s="7" t="inlineStr"/>
     </row>
@@ -3506,7 +3960,11 @@
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
       <c r="K102" s="7" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
@@ -3546,7 +4004,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J103" s="7" t="inlineStr"/>
       <c r="K103" s="7" t="inlineStr"/>
     </row>
@@ -3587,7 +4049,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J104" s="7" t="inlineStr"/>
       <c r="K104" s="7" t="inlineStr"/>
     </row>
@@ -3629,8 +4095,16 @@
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr"/>
-      <c r="J105" s="7" t="inlineStr"/>
-      <c r="K105" s="7" t="inlineStr"/>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Comment sécuriser le revenu des éleveurs tout en garantissant la pérennité de la filière ? Retour sur notre table ronde du 17 décembre dernier avec Jean Sorhouet, Président de l’OP bovine de Lur Berri qui présente la démarche de contractualisation de la coopérative permettant un débouché rémunérateur pour l’éleveur, avec une connaissance du prix de reprise du bovin dès sa mise en place. Une visibilité qui présente un atout indéniable pour les partenaires bancaires."</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="8" t="n">
@@ -3669,9 +4143,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J106" s="7" t="inlineStr"/>
-      <c r="K106" s="7" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>très ancienne campagne</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -3710,7 +4192,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr"/>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J107" s="7" t="inlineStr"/>
       <c r="K107" s="7" t="inlineStr"/>
     </row>
@@ -3752,7 +4238,11 @@
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr"/>
-      <c r="J108" s="7" t="inlineStr"/>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
       <c r="K108" s="7" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
@@ -3793,8 +4283,17 @@
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr"/>
-      <c r="J109" s="7" t="inlineStr"/>
-      <c r="K109" s="7" t="inlineStr"/>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Découverte de toutes les étapes de préparation du Foie Gras avec Nicolas.
+Nos deux chefs Pierre Chomet et Matthias Marc nous présentent toutes les étapes de la préparation du Foie Gras  en compagnie de Nicolas Fort, chef cuisinier dans les Landes. Direction les cuisines pour découvrir tout le savoir-faire de la filière et la préparation du Foie Gras comme vous ne l'avez jamais vu !"</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="8" t="n">
@@ -3835,7 +4334,11 @@
       </c>
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="7" t="inlineStr"/>
-      <c r="K110" s="7" t="inlineStr"/>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="8" t="n">
@@ -3875,7 +4378,11 @@
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr"/>
-      <c r="J111" s="7" t="inlineStr"/>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
       <c r="K111" s="7" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
@@ -3917,7 +4424,11 @@
       </c>
       <c r="I112" s="7" t="inlineStr"/>
       <c r="J112" s="7" t="inlineStr"/>
-      <c r="K112" s="7" t="inlineStr"/>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="8" t="n">
@@ -3958,7 +4469,11 @@
       </c>
       <c r="I113" s="7" t="inlineStr"/>
       <c r="J113" s="7" t="inlineStr"/>
-      <c r="K113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="8" t="n">
@@ -3999,7 +4514,11 @@
       </c>
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="7" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr"/>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="8" t="n">
@@ -4040,7 +4559,11 @@
       </c>
       <c r="I115" s="7" t="inlineStr"/>
       <c r="J115" s="7" t="inlineStr"/>
-      <c r="K115" s="7" t="inlineStr"/>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="8" t="n">
@@ -4080,8 +4603,16 @@
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr"/>
-      <c r="J116" s="7" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Partez à la rencontre des professionnels qui ont dit « Oui à la Volaille Française ! ». Dans cet épisode, retrouvez Stéphanie Sardain et Vincent Dumontet, gérants du commerce « Au Marché de la Volaille » à Mansle en Charente. Ils nous expliquent pourquoi ils ont fait le choix de la Volaille Française."</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="8" t="n">
@@ -4122,7 +4653,11 @@
       </c>
       <c r="I117" s="7" t="inlineStr"/>
       <c r="J117" s="7" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="8" t="n">
@@ -4161,7 +4696,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr"/>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J118" s="7" t="inlineStr"/>
       <c r="K118" s="7" t="inlineStr"/>
     </row>
@@ -4204,7 +4743,11 @@
       </c>
       <c r="I119" s="7" t="inlineStr"/>
       <c r="J119" s="7" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="8" t="n">
@@ -4244,7 +4787,11 @@
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr"/>
-      <c r="J120" s="7" t="inlineStr"/>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
       <c r="K120" s="7" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
@@ -4284,7 +4831,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I121" s="7" t="inlineStr"/>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J121" s="7" t="inlineStr"/>
       <c r="K121" s="7" t="inlineStr"/>
     </row>
@@ -4326,8 +4877,17 @@
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr"/>
-      <c r="J122" s="7" t="inlineStr"/>
-      <c r="K122" s="7" t="inlineStr"/>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Description: "De "Lou Maigret" au Magret : la naissance d'une star de la gastronomie française.
+Un entretien de Jean-Caude Narcy avec André Daguin."</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="8" t="n">
@@ -4368,7 +4928,11 @@
       </c>
       <c r="I123" s="7" t="inlineStr"/>
       <c r="J123" s="7" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>Déjà mentionné plus haut</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="8" t="n">
@@ -4408,8 +4972,20 @@
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr"/>
-      <c r="J124" s="7" t="inlineStr"/>
-      <c r="K124" s="7" t="inlineStr"/>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Interview d'Antoine Herth, Député du Bas-Rhin, Membre de la commission des affaires économiques.
+Antoine Herth intervient sur : 
+la compétitivité de la filière élevage et viande ; 
+la démarche Viandes de France
+la mention de l'origine sur les plats préparés à base de viande."</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="8" t="n">
@@ -4490,8 +5066,16 @@
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr"/>
-      <c r="J126" s="7" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr"/>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Partez à la rencontre des professionnels qui ont dit « Oui à la Volaille Française ! ». Dans cet épisode, retrouvez Boris Tillot, responsable d’activité chez Estiveau (Groupe Le Saint). Il nous explique pourquoi il a fait le choix de la Volaille Française."</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="8" t="n">
@@ -4531,7 +5115,11 @@
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr"/>
-      <c r="J127" s="7" t="inlineStr"/>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
       <c r="K127" s="7" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
@@ -4572,8 +5160,16 @@
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr"/>
-      <c r="J128" s="7" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr"/>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Interview de Bruno Lemaire, Député de la 1ère circonscription de l'Eure et ancien Ministre de l'Agriculture."</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="8" t="n">
@@ -4613,8 +5209,16 @@
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr"/>
-      <c r="J129" s="7" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="8" t="n">
@@ -4654,8 +5258,16 @@
         </is>
       </c>
       <c r="I130" s="7" t="inlineStr"/>
-      <c r="J130" s="7" t="inlineStr"/>
-      <c r="K130" s="7" t="inlineStr"/>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="8" t="n">
@@ -4695,8 +5307,16 @@
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr"/>
-      <c r="J131" s="7" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Déjà mentionné plus haut</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="8" t="n">
@@ -4736,7 +5356,11 @@
         </is>
       </c>
       <c r="I132" s="7" t="inlineStr"/>
-      <c r="J132" s="7" t="inlineStr"/>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>eleveur ou agriculteur</t>
+        </is>
+      </c>
       <c r="K132" s="7" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
@@ -4777,7 +5401,11 @@
         </is>
       </c>
       <c r="I133" s="7" t="inlineStr"/>
-      <c r="J133" s="7" t="inlineStr"/>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>eleveur ou agriculteur</t>
+        </is>
+      </c>
       <c r="K133" s="7" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
@@ -4818,7 +5446,11 @@
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr"/>
-      <c r="J134" s="7" t="inlineStr"/>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>eleveur ou agriculteur</t>
+        </is>
+      </c>
       <c r="K134" s="7" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
@@ -4859,7 +5491,11 @@
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr"/>
-      <c r="J135" s="7" t="inlineStr"/>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>eleveur ou agriculteur</t>
+        </is>
+      </c>
       <c r="K135" s="7" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
@@ -4900,8 +5536,16 @@
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr"/>
-      <c r="J136" s="7" t="inlineStr"/>
-      <c r="K136" s="7" t="inlineStr"/>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>chef ou restaurateur</t>
+        </is>
+      </c>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Découvrez la vidéo des recettes de Clotilde Jacoulot, Meilleur Ouvrier de France Primeur qui allient avec délice le Foie Gras et Magret aux fruits et légumes. Pas à pas, réalisez ces amuse-bouche au Foie Gras et Magret, pour un apéro gourmet qui ravira vos convives !"</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="8" t="n">
@@ -4940,9 +5584,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I137" s="7" t="inlineStr"/>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J137" s="7" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="8" t="n">
@@ -4981,9 +5633,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I138" s="7" t="inlineStr"/>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J138" s="7" t="inlineStr"/>
-      <c r="K138" s="7" t="inlineStr"/>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="8" t="n">
@@ -5022,9 +5682,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I139" s="7" t="inlineStr"/>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J139" s="7" t="inlineStr"/>
-      <c r="K139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="8" t="n">
@@ -5063,9 +5731,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I140" s="7" t="inlineStr"/>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J140" s="7" t="inlineStr"/>
-      <c r="K140" s="7" t="inlineStr"/>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="8" t="n">
@@ -5146,8 +5822,17 @@
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr"/>
-      <c r="J142" s="7" t="inlineStr"/>
-      <c r="K142" s="7" t="inlineStr"/>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>Description: "Blogueur culinaire depuis 2005, Dorian est un cuisinier dont la gourmandise pour le salé n’a d’égal que la curiosité et l’amour pour des saveurs du monde. C’est sans ambiguïté qu’il crée son blog, il y a près de 10 ans, pour partager, certes,  mais apprendre avant tout au contact d’une blogosphère très féminine et des chefs cuisiniers. 
+Ce "carnassier" respectueux de la viande – dont la franchise et le goût pour la convivialité séduisent – est l’auteur d’ouvrages culinaires et de près de 3 000 recettes sur son blog."</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="8" t="n">
@@ -5187,8 +5872,16 @@
         </is>
       </c>
       <c r="I143" s="7" t="inlineStr"/>
-      <c r="J143" s="7" t="inlineStr"/>
-      <c r="K143" s="7" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="8" t="n">
@@ -5228,8 +5921,16 @@
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr"/>
-      <c r="J144" s="7" t="inlineStr"/>
-      <c r="K144" s="7" t="inlineStr"/>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>blog</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="8" t="n">
@@ -5269,8 +5970,16 @@
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr"/>
-      <c r="J145" s="7" t="inlineStr"/>
-      <c r="K145" s="7" t="inlineStr"/>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>description: "Partez à la rencontre des professionnels qui ont dit « Oui à la Volaille Française ! ». Dans cet épisode, retrouvez Emmanuel Coyaud, directeur général de Tradition et Gourmandises (94), qui nous explique pourquoi il a fait le choix de la Volaille Française."</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="8" t="n">
@@ -5310,8 +6019,16 @@
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr"/>
-      <c r="J146" s="7" t="inlineStr"/>
-      <c r="K146" s="7" t="inlineStr"/>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>Déjà mentionné plus haut</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="8" t="n">
@@ -5350,7 +6067,11 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I147" s="7" t="inlineStr"/>
+      <c r="I147" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J147" s="7" t="inlineStr"/>
       <c r="K147" s="7" t="inlineStr"/>
     </row>
@@ -5392,8 +6113,16 @@
         </is>
       </c>
       <c r="I148" s="7" t="inlineStr"/>
-      <c r="J148" s="7" t="inlineStr"/>
-      <c r="K148" s="7" t="inlineStr"/>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K148" s="7" t="inlineStr">
+        <is>
+          <t>description: "Interview d'Eric Andrieu, Député européen de la circonscription Sud-Ouest, Membre de la Commission de l'agriculture et du développement rural."</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="8" t="n">
@@ -5433,8 +6162,16 @@
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr"/>
-      <c r="J149" s="7" t="inlineStr"/>
-      <c r="K149" s="7" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>description: "Pour penser le fromage autrement : du fromage en dessert, une histoire racontée par Eric Birlouez, sociologue et spécialiste de l’Histoire de l’alimentation, Xavier Thuret, MOF Fromager, Jean-Charles Karmann, confiseur de fromages."</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="8" t="n">
@@ -5474,8 +6211,16 @@
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr"/>
-      <c r="J150" s="7" t="inlineStr"/>
-      <c r="K150" s="7" t="inlineStr"/>
+      <c r="J150" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K150" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="8" t="n">
@@ -5515,8 +6260,16 @@
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr"/>
-      <c r="J151" s="7" t="inlineStr"/>
-      <c r="K151" s="7" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="8" t="n">
@@ -5556,8 +6309,16 @@
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr"/>
-      <c r="J152" s="7" t="inlineStr"/>
-      <c r="K152" s="7" t="inlineStr"/>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>juste un prénom</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="8" t="n">
@@ -5597,8 +6358,16 @@
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr"/>
-      <c r="J153" s="7" t="inlineStr"/>
-      <c r="K153" s="7" t="inlineStr"/>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>description: "Découverte de cet ambassadeur de la gastronomie française avec Fabien Chevalier, Président du Cercle des amoureux du Foie Gras."</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="8" t="n">
@@ -5638,8 +6407,16 @@
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
-      <c r="J154" s="7" t="inlineStr"/>
-      <c r="K154" s="7" t="inlineStr"/>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>Juste un titre</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="8" t="n">
@@ -5679,8 +6456,16 @@
         </is>
       </c>
       <c r="I155" s="7" t="inlineStr"/>
-      <c r="J155" s="7" t="inlineStr"/>
-      <c r="K155" s="7" t="inlineStr"/>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>Musique originale par Florent De Maria, Jérémy Villecourt, Pierre Sendrané</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="8" t="n">
@@ -6787,7 +7572,11 @@
       </c>
       <c r="I182" s="7" t="inlineStr"/>
       <c r="J182" s="7" t="inlineStr"/>
-      <c r="K182" s="7" t="inlineStr"/>
+      <c r="K182" s="7" t="inlineStr">
+        <is>
+          <t>politicien</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="8" t="n">
@@ -7851,9 +8640,21 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I208" s="7" t="inlineStr"/>
-      <c r="J208" s="7" t="inlineStr"/>
-      <c r="K208" s="7" t="inlineStr"/>
+      <c r="I208" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>createur de contenu (youtubeur</t>
+        </is>
+      </c>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>Vidéo de Mister V et co (Écrit par Mister V, Vincent Tirel et Freddy Gladieux)</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="8" t="n">
@@ -8140,7 +8941,11 @@
       </c>
       <c r="I215" s="7" t="inlineStr"/>
       <c r="J215" s="7" t="inlineStr"/>
-      <c r="K215" s="7" t="inlineStr"/>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>déjà mentionné plus haut</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="30" customHeight="1">
       <c r="A216" s="8" t="n">
@@ -8261,9 +9066,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I218" s="7" t="inlineStr"/>
+      <c r="I218" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
       <c r="J218" s="7" t="inlineStr"/>
-      <c r="K218" s="7" t="inlineStr"/>
+      <c r="K218" s="7" t="inlineStr">
+        <is>
+          <t>Mister V' est un créateur</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="30" customHeight="1">
       <c r="A219" s="8" t="n">
@@ -8302,9 +9115,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I219" s="7" t="inlineStr"/>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
       <c r="J219" s="7" t="inlineStr"/>
-      <c r="K219" s="7" t="inlineStr"/>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>Mister V' est un créateur</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="30" customHeight="1">
       <c r="A220" s="8" t="n">
@@ -8343,9 +9164,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I220" s="7" t="inlineStr"/>
+      <c r="I220" s="7" t="inlineStr">
+        <is>
+          <t>c'est un createur</t>
+        </is>
+      </c>
       <c r="J220" s="7" t="inlineStr"/>
-      <c r="K220" s="7" t="inlineStr"/>
+      <c r="K220" s="7" t="inlineStr">
+        <is>
+          <t>Mister V' est un créateur</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="8" t="n">
@@ -8468,7 +9297,11 @@
       </c>
       <c r="I223" s="7" t="inlineStr"/>
       <c r="J223" s="7" t="inlineStr"/>
-      <c r="K223" s="7" t="inlineStr"/>
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>politicien</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="8" t="n">
@@ -8630,9 +9463,17 @@
           <t>voir la video</t>
         </is>
       </c>
-      <c r="I227" s="7" t="inlineStr"/>
+      <c r="I227" s="7" t="inlineStr">
+        <is>
+          <t>c'est un nom de serie ou de campagne</t>
+        </is>
+      </c>
       <c r="J227" s="7" t="inlineStr"/>
-      <c r="K227" s="7" t="inlineStr"/>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>titre d'une pub</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="8" t="n">
